--- a/clients/healthcare-demo-new/19-template-instantiation-source-corpus/01-template-workbooks/HC_KPI_STARS_HEDIS_CATALOG.xlsx
+++ b/clients/healthcare-demo-new/19-template-instantiation-source-corpus/01-template-workbooks/HC_KPI_STARS_HEDIS_CATALOG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Catalog" sheetId="1" r:id="R0e8512edaa2449ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Catalog" sheetId="1" r:id="Ra20d4b257d3245c9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -315,12 +315,12 @@
     <x:col min="1" max="1" width="11.5600004196167" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="33.11000061035156" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="16.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="52.439998626708984" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12.5600004196167" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="17.440000534057617" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="17.440000534057617" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="34.439998626708984" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="14.329999923706055" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -361,13 +361,13 @@
         <x:v>KPI-HCDN-0001</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>Medication adherence measure 0001</x:v>
+        <x:v>HEDIS medication adherence measure 0001</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
         <x:v>Revenue Cycle</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str">
         <x:v>range</x:v>
@@ -393,7 +393,7 @@
         <x:v>KPI-HCDN-0002</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0002</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0002</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
         <x:v>Patient Access</x:v>
@@ -425,7 +425,7 @@
         <x:v>KPI-HCDN-0003</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>Breast cancer screening measure 0003</x:v>
+        <x:v>HEDIS breast cancer screening measure 0003</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
         <x:v>Interoperability</x:v>
@@ -542,7 +542,7 @@
         <x:v>DATA-HCDN-00007</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J7" s="11" t="str">
         <x:v>SRC-HCDN-KPI-007</x:v>
@@ -574,7 +574,7 @@
         <x:v>DATA-HCDN-00008</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J8" s="11" t="str">
         <x:v>SRC-HCDN-KPI-008</x:v>
@@ -591,7 +591,7 @@
         <x:v>Utilization Management</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -606,7 +606,7 @@
         <x:v>DATA-HCDN-00009</x:v>
       </x:c>
       <x:c r="I9" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str">
         <x:v>SRC-HCDN-KPI-009</x:v>
@@ -623,7 +623,7 @@
         <x:v>Member Services</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str">
         <x:v>withheld</x:v>
@@ -638,7 +638,7 @@
         <x:v>DATA-HCDN-00010</x:v>
       </x:c>
       <x:c r="I10" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J10" s="11" t="str">
         <x:v>SRC-HCDN-KPI-010</x:v>
@@ -670,7 +670,7 @@
         <x:v>DATA-HCDN-00011</x:v>
       </x:c>
       <x:c r="I11" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str">
         <x:v>SRC-HCDN-KPI-011</x:v>
@@ -702,7 +702,7 @@
         <x:v>DATA-HCDN-00012</x:v>
       </x:c>
       <x:c r="I12" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J12" s="11" t="str">
         <x:v>SRC-HCDN-KPI-012</x:v>
@@ -734,7 +734,7 @@
         <x:v>DATA-HCDN-00013</x:v>
       </x:c>
       <x:c r="I13" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J13" s="11" t="str">
         <x:v>SRC-HCDN-KPI-013</x:v>
@@ -766,7 +766,7 @@
         <x:v>DATA-HCDN-00014</x:v>
       </x:c>
       <x:c r="I14" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J14" s="11" t="str">
         <x:v>SRC-HCDN-KPI-014</x:v>
@@ -798,7 +798,7 @@
         <x:v>DATA-HCDN-00015</x:v>
       </x:c>
       <x:c r="I15" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J15" s="11" t="str">
         <x:v>SRC-HCDN-KPI-015</x:v>
@@ -830,7 +830,7 @@
         <x:v>DATA-HCDN-00016</x:v>
       </x:c>
       <x:c r="I16" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J16" s="11" t="str">
         <x:v>SRC-HCDN-KPI-016</x:v>
@@ -847,7 +847,7 @@
         <x:v>Digital Front Door</x:v>
       </x:c>
       <x:c r="D17" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str">
         <x:v>range</x:v>
@@ -862,7 +862,7 @@
         <x:v>DATA-HCDN-00017</x:v>
       </x:c>
       <x:c r="I17" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J17" s="11" t="str">
         <x:v>SRC-HCDN-KPI-017</x:v>
@@ -879,7 +879,7 @@
         <x:v>Contact Center</x:v>
       </x:c>
       <x:c r="D18" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str">
         <x:v>indexed</x:v>
@@ -894,7 +894,7 @@
         <x:v>DATA-HCDN-00018</x:v>
       </x:c>
       <x:c r="I18" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J18" s="11" t="str">
         <x:v>SRC-HCDN-KPI-018</x:v>
@@ -926,7 +926,7 @@
         <x:v>DATA-HCDN-00019</x:v>
       </x:c>
       <x:c r="I19" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J19" s="11" t="str">
         <x:v>SRC-HCDN-KPI-019</x:v>
@@ -958,7 +958,7 @@
         <x:v>DATA-HCDN-00020</x:v>
       </x:c>
       <x:c r="I20" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J20" s="11" t="str">
         <x:v>SRC-HCDN-KPI-020</x:v>
@@ -990,7 +990,7 @@
         <x:v>DATA-HCDN-00021</x:v>
       </x:c>
       <x:c r="I21" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J21" s="11" t="str">
         <x:v>SRC-HCDN-KPI-021</x:v>
@@ -1022,7 +1022,7 @@
         <x:v>DATA-HCDN-00022</x:v>
       </x:c>
       <x:c r="I22" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J22" s="11" t="str">
         <x:v>SRC-HCDN-KPI-022</x:v>
@@ -1054,7 +1054,7 @@
         <x:v>DATA-HCDN-00023</x:v>
       </x:c>
       <x:c r="I23" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J23" s="11" t="str">
         <x:v>SRC-HCDN-KPI-023</x:v>
@@ -1086,7 +1086,7 @@
         <x:v>DATA-HCDN-00024</x:v>
       </x:c>
       <x:c r="I24" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J24" s="11" t="str">
         <x:v>SRC-HCDN-KPI-024</x:v>
@@ -1103,7 +1103,7 @@
         <x:v>Pharmacy</x:v>
       </x:c>
       <x:c r="D25" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str">
         <x:v>withheld</x:v>
@@ -1118,7 +1118,7 @@
         <x:v>DATA-HCDN-00025</x:v>
       </x:c>
       <x:c r="I25" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J25" s="11" t="str">
         <x:v>SRC-HCDN-KPI-025</x:v>
@@ -1135,7 +1135,7 @@
         <x:v>Oncology</x:v>
       </x:c>
       <x:c r="D26" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str">
         <x:v>exact</x:v>
@@ -1150,7 +1150,7 @@
         <x:v>DATA-HCDN-00026</x:v>
       </x:c>
       <x:c r="I26" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J26" s="11" t="str">
         <x:v>SRC-HCDN-KPI-026</x:v>
@@ -1182,7 +1182,7 @@
         <x:v>DATA-HCDN-00027</x:v>
       </x:c>
       <x:c r="I27" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J27" s="11" t="str">
         <x:v>SRC-HCDN-KPI-027</x:v>
@@ -1214,7 +1214,7 @@
         <x:v>DATA-HCDN-00028</x:v>
       </x:c>
       <x:c r="I28" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J28" s="11" t="str">
         <x:v>SRC-HCDN-KPI-028</x:v>
@@ -1246,7 +1246,7 @@
         <x:v>DATA-HCDN-00029</x:v>
       </x:c>
       <x:c r="I29" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J29" s="11" t="str">
         <x:v>SRC-HCDN-KPI-029</x:v>
@@ -1278,7 +1278,7 @@
         <x:v>DATA-HCDN-00030</x:v>
       </x:c>
       <x:c r="I30" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J30" s="11" t="str">
         <x:v>SRC-HCDN-KPI-030</x:v>
@@ -1310,7 +1310,7 @@
         <x:v>DATA-HCDN-00031</x:v>
       </x:c>
       <x:c r="I31" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J31" s="11" t="str">
         <x:v>SRC-HCDN-KPI-031</x:v>
@@ -1342,7 +1342,7 @@
         <x:v>DATA-HCDN-00032</x:v>
       </x:c>
       <x:c r="I32" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J32" s="11" t="str">
         <x:v>SRC-HCDN-KPI-032</x:v>
@@ -1359,7 +1359,7 @@
         <x:v>Technology</x:v>
       </x:c>
       <x:c r="D33" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E33" s="11" t="str">
         <x:v>indexed</x:v>
@@ -1374,7 +1374,7 @@
         <x:v>DATA-HCDN-00033</x:v>
       </x:c>
       <x:c r="I33" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J33" s="11" t="str">
         <x:v>SRC-HCDN-KPI-033</x:v>
@@ -1385,13 +1385,13 @@
         <x:v>KPI-HCDN-0033</x:v>
       </x:c>
       <x:c r="B34" s="11" t="str">
-        <x:v>Medication adherence measure 0033</x:v>
+        <x:v>HEDIS medication adherence measure 0033</x:v>
       </x:c>
       <x:c r="C34" s="11" t="str">
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D34" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E34" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -1406,7 +1406,7 @@
         <x:v>DATA-HCDN-00034</x:v>
       </x:c>
       <x:c r="I34" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J34" s="11" t="str">
         <x:v>SRC-HCDN-KPI-034</x:v>
@@ -1417,7 +1417,7 @@
         <x:v>KPI-HCDN-0034</x:v>
       </x:c>
       <x:c r="B35" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0034</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0034</x:v>
       </x:c>
       <x:c r="C35" s="11" t="str">
         <x:v>Procurement</x:v>
@@ -1438,7 +1438,7 @@
         <x:v>DATA-HCDN-00035</x:v>
       </x:c>
       <x:c r="I35" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J35" s="11" t="str">
         <x:v>SRC-HCDN-KPI-035</x:v>
@@ -1449,7 +1449,7 @@
         <x:v>KPI-HCDN-0035</x:v>
       </x:c>
       <x:c r="B36" s="11" t="str">
-        <x:v>Breast cancer screening measure 0035</x:v>
+        <x:v>HEDIS breast cancer screening measure 0035</x:v>
       </x:c>
       <x:c r="C36" s="11" t="str">
         <x:v>HR</x:v>
@@ -1470,7 +1470,7 @@
         <x:v>DATA-HCDN-00036</x:v>
       </x:c>
       <x:c r="I36" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J36" s="11" t="str">
         <x:v>SRC-HCDN-KPI-036</x:v>
@@ -1502,7 +1502,7 @@
         <x:v>DATA-HCDN-00037</x:v>
       </x:c>
       <x:c r="I37" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J37" s="11" t="str">
         <x:v>SRC-HCDN-KPI-037</x:v>
@@ -1534,7 +1534,7 @@
         <x:v>DATA-HCDN-00038</x:v>
       </x:c>
       <x:c r="I38" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J38" s="11" t="str">
         <x:v>SRC-HCDN-KPI-038</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>DATA-HCDN-00039</x:v>
       </x:c>
       <x:c r="I39" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J39" s="11" t="str">
         <x:v>SRC-HCDN-KPI-039</x:v>
@@ -1598,7 +1598,7 @@
         <x:v>DATA-HCDN-00040</x:v>
       </x:c>
       <x:c r="I40" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J40" s="11" t="str">
         <x:v>SRC-HCDN-KPI-040</x:v>
@@ -1615,7 +1615,7 @@
         <x:v>Value-Based Care</x:v>
       </x:c>
       <x:c r="D41" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E41" s="11" t="str">
         <x:v>exact</x:v>
@@ -1630,7 +1630,7 @@
         <x:v>DATA-HCDN-00041</x:v>
       </x:c>
       <x:c r="I41" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J41" s="11" t="str">
         <x:v>SRC-HCDN-KPI-041</x:v>
@@ -1647,7 +1647,7 @@
         <x:v>Clinical Operations</x:v>
       </x:c>
       <x:c r="D42" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E42" s="11" t="str">
         <x:v>range</x:v>
@@ -1662,7 +1662,7 @@
         <x:v>DATA-HCDN-00042</x:v>
       </x:c>
       <x:c r="I42" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J42" s="11" t="str">
         <x:v>SRC-HCDN-KPI-042</x:v>
@@ -1871,7 +1871,7 @@
         <x:v>Claims Operations</x:v>
       </x:c>
       <x:c r="D49" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E49" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -1886,7 +1886,7 @@
         <x:v>DATA-HCDN-00049</x:v>
       </x:c>
       <x:c r="I49" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J49" s="11" t="str">
         <x:v>SRC-HCDN-KPI-049</x:v>
@@ -1903,7 +1903,7 @@
         <x:v>Utilization Management</x:v>
       </x:c>
       <x:c r="D50" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E50" s="11" t="str">
         <x:v>withheld</x:v>
@@ -1918,7 +1918,7 @@
         <x:v>DATA-HCDN-00050</x:v>
       </x:c>
       <x:c r="I50" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J50" s="11" t="str">
         <x:v>SRC-HCDN-KPI-050</x:v>
@@ -1950,7 +1950,7 @@
         <x:v>DATA-HCDN-00051</x:v>
       </x:c>
       <x:c r="I51" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J51" s="11" t="str">
         <x:v>SRC-HCDN-KPI-051</x:v>
@@ -1982,7 +1982,7 @@
         <x:v>DATA-HCDN-00052</x:v>
       </x:c>
       <x:c r="I52" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J52" s="11" t="str">
         <x:v>SRC-HCDN-KPI-052</x:v>
@@ -2014,7 +2014,7 @@
         <x:v>DATA-HCDN-00053</x:v>
       </x:c>
       <x:c r="I53" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J53" s="11" t="str">
         <x:v>SRC-HCDN-KPI-053</x:v>
@@ -2046,7 +2046,7 @@
         <x:v>DATA-HCDN-00054</x:v>
       </x:c>
       <x:c r="I54" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J54" s="11" t="str">
         <x:v>SRC-HCDN-KPI-054</x:v>
@@ -2078,7 +2078,7 @@
         <x:v>DATA-HCDN-00055</x:v>
       </x:c>
       <x:c r="I55" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J55" s="11" t="str">
         <x:v>SRC-HCDN-KPI-055</x:v>
@@ -2110,7 +2110,7 @@
         <x:v>DATA-HCDN-00056</x:v>
       </x:c>
       <x:c r="I56" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J56" s="11" t="str">
         <x:v>SRC-HCDN-KPI-056</x:v>
@@ -2127,7 +2127,7 @@
         <x:v>Payer Contracting</x:v>
       </x:c>
       <x:c r="D57" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E57" s="11" t="str">
         <x:v>range</x:v>
@@ -2142,7 +2142,7 @@
         <x:v>DATA-HCDN-00057</x:v>
       </x:c>
       <x:c r="I57" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J57" s="11" t="str">
         <x:v>SRC-HCDN-KPI-057</x:v>
@@ -2159,7 +2159,7 @@
         <x:v>Digital Front Door</x:v>
       </x:c>
       <x:c r="D58" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E58" s="11" t="str">
         <x:v>indexed</x:v>
@@ -2174,7 +2174,7 @@
         <x:v>DATA-HCDN-00058</x:v>
       </x:c>
       <x:c r="I58" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J58" s="11" t="str">
         <x:v>SRC-HCDN-KPI-058</x:v>
@@ -2206,7 +2206,7 @@
         <x:v>DATA-HCDN-00059</x:v>
       </x:c>
       <x:c r="I59" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J59" s="11" t="str">
         <x:v>SRC-HCDN-KPI-059</x:v>
@@ -2238,7 +2238,7 @@
         <x:v>DATA-HCDN-00060</x:v>
       </x:c>
       <x:c r="I60" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J60" s="11" t="str">
         <x:v>SRC-HCDN-KPI-060</x:v>
@@ -2270,7 +2270,7 @@
         <x:v>DATA-HCDN-00061</x:v>
       </x:c>
       <x:c r="I61" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J61" s="11" t="str">
         <x:v>SRC-HCDN-KPI-061</x:v>
@@ -2302,7 +2302,7 @@
         <x:v>DATA-HCDN-00062</x:v>
       </x:c>
       <x:c r="I62" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J62" s="11" t="str">
         <x:v>SRC-HCDN-KPI-062</x:v>
@@ -2334,7 +2334,7 @@
         <x:v>DATA-HCDN-00063</x:v>
       </x:c>
       <x:c r="I63" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J63" s="11" t="str">
         <x:v>SRC-HCDN-KPI-063</x:v>
@@ -2366,7 +2366,7 @@
         <x:v>DATA-HCDN-00064</x:v>
       </x:c>
       <x:c r="I64" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J64" s="11" t="str">
         <x:v>SRC-HCDN-KPI-064</x:v>
@@ -2383,7 +2383,7 @@
         <x:v>Lab</x:v>
       </x:c>
       <x:c r="D65" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E65" s="11" t="str">
         <x:v>withheld</x:v>
@@ -2398,7 +2398,7 @@
         <x:v>DATA-HCDN-00065</x:v>
       </x:c>
       <x:c r="I65" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J65" s="11" t="str">
         <x:v>SRC-HCDN-KPI-065</x:v>
@@ -2409,13 +2409,13 @@
         <x:v>KPI-HCDN-0065</x:v>
       </x:c>
       <x:c r="B66" s="11" t="str">
-        <x:v>Medication adherence measure 0065</x:v>
+        <x:v>HEDIS medication adherence measure 0065</x:v>
       </x:c>
       <x:c r="C66" s="11" t="str">
         <x:v>Pharmacy</x:v>
       </x:c>
       <x:c r="D66" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E66" s="11" t="str">
         <x:v>exact</x:v>
@@ -2430,7 +2430,7 @@
         <x:v>DATA-HCDN-00066</x:v>
       </x:c>
       <x:c r="I66" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J66" s="11" t="str">
         <x:v>SRC-HCDN-KPI-066</x:v>
@@ -2441,7 +2441,7 @@
         <x:v>KPI-HCDN-0066</x:v>
       </x:c>
       <x:c r="B67" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0066</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0066</x:v>
       </x:c>
       <x:c r="C67" s="11" t="str">
         <x:v>Oncology</x:v>
@@ -2462,7 +2462,7 @@
         <x:v>DATA-HCDN-00067</x:v>
       </x:c>
       <x:c r="I67" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J67" s="11" t="str">
         <x:v>SRC-HCDN-KPI-067</x:v>
@@ -2473,7 +2473,7 @@
         <x:v>KPI-HCDN-0067</x:v>
       </x:c>
       <x:c r="B68" s="11" t="str">
-        <x:v>Breast cancer screening measure 0067</x:v>
+        <x:v>HEDIS breast cancer screening measure 0067</x:v>
       </x:c>
       <x:c r="C68" s="11" t="str">
         <x:v>Cardiology</x:v>
@@ -2494,7 +2494,7 @@
         <x:v>DATA-HCDN-00068</x:v>
       </x:c>
       <x:c r="I68" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J68" s="11" t="str">
         <x:v>SRC-HCDN-KPI-068</x:v>
@@ -2526,7 +2526,7 @@
         <x:v>DATA-HCDN-00069</x:v>
       </x:c>
       <x:c r="I69" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J69" s="11" t="str">
         <x:v>SRC-HCDN-KPI-069</x:v>
@@ -2558,7 +2558,7 @@
         <x:v>DATA-HCDN-00070</x:v>
       </x:c>
       <x:c r="I70" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J70" s="11" t="str">
         <x:v>SRC-HCDN-KPI-070</x:v>
@@ -2590,7 +2590,7 @@
         <x:v>DATA-HCDN-00071</x:v>
       </x:c>
       <x:c r="I71" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J71" s="11" t="str">
         <x:v>SRC-HCDN-KPI-071</x:v>
@@ -2622,7 +2622,7 @@
         <x:v>DATA-HCDN-00072</x:v>
       </x:c>
       <x:c r="I72" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J72" s="11" t="str">
         <x:v>SRC-HCDN-KPI-072</x:v>
@@ -2639,7 +2639,7 @@
         <x:v>AI Transformation</x:v>
       </x:c>
       <x:c r="D73" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E73" s="11" t="str">
         <x:v>indexed</x:v>
@@ -2654,7 +2654,7 @@
         <x:v>DATA-HCDN-00073</x:v>
       </x:c>
       <x:c r="I73" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J73" s="11" t="str">
         <x:v>SRC-HCDN-KPI-073</x:v>
@@ -2671,7 +2671,7 @@
         <x:v>Technology</x:v>
       </x:c>
       <x:c r="D74" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E74" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -2686,7 +2686,7 @@
         <x:v>DATA-HCDN-00074</x:v>
       </x:c>
       <x:c r="I74" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J74" s="11" t="str">
         <x:v>SRC-HCDN-KPI-074</x:v>
@@ -2718,7 +2718,7 @@
         <x:v>DATA-HCDN-00075</x:v>
       </x:c>
       <x:c r="I75" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J75" s="11" t="str">
         <x:v>SRC-HCDN-KPI-075</x:v>
@@ -2750,7 +2750,7 @@
         <x:v>DATA-HCDN-00076</x:v>
       </x:c>
       <x:c r="I76" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J76" s="11" t="str">
         <x:v>SRC-HCDN-KPI-076</x:v>
@@ -2782,7 +2782,7 @@
         <x:v>DATA-HCDN-00077</x:v>
       </x:c>
       <x:c r="I77" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J77" s="11" t="str">
         <x:v>SRC-HCDN-KPI-077</x:v>
@@ -2814,7 +2814,7 @@
         <x:v>DATA-HCDN-00078</x:v>
       </x:c>
       <x:c r="I78" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J78" s="11" t="str">
         <x:v>SRC-HCDN-KPI-078</x:v>
@@ -2846,7 +2846,7 @@
         <x:v>DATA-HCDN-00079</x:v>
       </x:c>
       <x:c r="I79" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J79" s="11" t="str">
         <x:v>SRC-HCDN-KPI-079</x:v>
@@ -2878,7 +2878,7 @@
         <x:v>DATA-HCDN-00080</x:v>
       </x:c>
       <x:c r="I80" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J80" s="11" t="str">
         <x:v>SRC-HCDN-KPI-080</x:v>
@@ -2895,7 +2895,7 @@
         <x:v>Provider Network</x:v>
       </x:c>
       <x:c r="D81" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E81" s="11" t="str">
         <x:v>exact</x:v>
@@ -2910,7 +2910,7 @@
         <x:v>DATA-HCDN-00081</x:v>
       </x:c>
       <x:c r="I81" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J81" s="11" t="str">
         <x:v>SRC-HCDN-KPI-081</x:v>
@@ -2927,7 +2927,7 @@
         <x:v>Value-Based Care</x:v>
       </x:c>
       <x:c r="D82" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E82" s="11" t="str">
         <x:v>range</x:v>
@@ -2942,7 +2942,7 @@
         <x:v>DATA-HCDN-00082</x:v>
       </x:c>
       <x:c r="I82" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J82" s="11" t="str">
         <x:v>SRC-HCDN-KPI-082</x:v>
@@ -2974,7 +2974,7 @@
         <x:v>DATA-HCDN-00083</x:v>
       </x:c>
       <x:c r="I83" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J83" s="11" t="str">
         <x:v>SRC-HCDN-KPI-083</x:v>
@@ -3006,7 +3006,7 @@
         <x:v>DATA-HCDN-00084</x:v>
       </x:c>
       <x:c r="I84" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J84" s="11" t="str">
         <x:v>SRC-HCDN-KPI-084</x:v>
@@ -3151,7 +3151,7 @@
         <x:v>Medicare Advantage</x:v>
       </x:c>
       <x:c r="D89" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E89" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -3183,7 +3183,7 @@
         <x:v>Claims Operations</x:v>
       </x:c>
       <x:c r="D90" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E90" s="11" t="str">
         <x:v>withheld</x:v>
@@ -3230,7 +3230,7 @@
         <x:v>DATA-HCDN-00091</x:v>
       </x:c>
       <x:c r="I91" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J91" s="11" t="str">
         <x:v>SRC-HCDN-KPI-091</x:v>
@@ -3262,7 +3262,7 @@
         <x:v>DATA-HCDN-00092</x:v>
       </x:c>
       <x:c r="I92" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J92" s="11" t="str">
         <x:v>SRC-HCDN-KPI-092</x:v>
@@ -3294,7 +3294,7 @@
         <x:v>DATA-HCDN-00093</x:v>
       </x:c>
       <x:c r="I93" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J93" s="11" t="str">
         <x:v>SRC-HCDN-KPI-093</x:v>
@@ -3326,7 +3326,7 @@
         <x:v>DATA-HCDN-00094</x:v>
       </x:c>
       <x:c r="I94" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J94" s="11" t="str">
         <x:v>SRC-HCDN-KPI-094</x:v>
@@ -3358,7 +3358,7 @@
         <x:v>DATA-HCDN-00095</x:v>
       </x:c>
       <x:c r="I95" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J95" s="11" t="str">
         <x:v>SRC-HCDN-KPI-095</x:v>
@@ -3390,7 +3390,7 @@
         <x:v>DATA-HCDN-00096</x:v>
       </x:c>
       <x:c r="I96" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J96" s="11" t="str">
         <x:v>SRC-HCDN-KPI-096</x:v>
@@ -3407,7 +3407,7 @@
         <x:v>Coding</x:v>
       </x:c>
       <x:c r="D97" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E97" s="11" t="str">
         <x:v>range</x:v>
@@ -3422,7 +3422,7 @@
         <x:v>DATA-HCDN-00097</x:v>
       </x:c>
       <x:c r="I97" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J97" s="11" t="str">
         <x:v>SRC-HCDN-KPI-001</x:v>
@@ -3433,13 +3433,13 @@
         <x:v>KPI-HCDN-0097</x:v>
       </x:c>
       <x:c r="B98" s="11" t="str">
-        <x:v>Medication adherence measure 0097</x:v>
+        <x:v>HEDIS medication adherence measure 0097</x:v>
       </x:c>
       <x:c r="C98" s="11" t="str">
         <x:v>Payer Contracting</x:v>
       </x:c>
       <x:c r="D98" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E98" s="11" t="str">
         <x:v>indexed</x:v>
@@ -3454,7 +3454,7 @@
         <x:v>DATA-HCDN-00098</x:v>
       </x:c>
       <x:c r="I98" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J98" s="11" t="str">
         <x:v>SRC-HCDN-KPI-002</x:v>
@@ -3465,7 +3465,7 @@
         <x:v>KPI-HCDN-0098</x:v>
       </x:c>
       <x:c r="B99" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0098</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0098</x:v>
       </x:c>
       <x:c r="C99" s="11" t="str">
         <x:v>Digital Front Door</x:v>
@@ -3486,7 +3486,7 @@
         <x:v>DATA-HCDN-00099</x:v>
       </x:c>
       <x:c r="I99" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J99" s="11" t="str">
         <x:v>SRC-HCDN-KPI-003</x:v>
@@ -3497,7 +3497,7 @@
         <x:v>KPI-HCDN-0099</x:v>
       </x:c>
       <x:c r="B100" s="11" t="str">
-        <x:v>Breast cancer screening measure 0099</x:v>
+        <x:v>HEDIS breast cancer screening measure 0099</x:v>
       </x:c>
       <x:c r="C100" s="11" t="str">
         <x:v>Contact Center</x:v>
@@ -3518,7 +3518,7 @@
         <x:v>DATA-HCDN-00100</x:v>
       </x:c>
       <x:c r="I100" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J100" s="11" t="str">
         <x:v>SRC-HCDN-KPI-004</x:v>
@@ -3550,7 +3550,7 @@
         <x:v>DATA-HCDN-00101</x:v>
       </x:c>
       <x:c r="I101" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J101" s="11" t="str">
         <x:v>SRC-HCDN-KPI-005</x:v>
@@ -3582,7 +3582,7 @@
         <x:v>DATA-HCDN-00102</x:v>
       </x:c>
       <x:c r="I102" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J102" s="11" t="str">
         <x:v>SRC-HCDN-KPI-006</x:v>
@@ -3614,7 +3614,7 @@
         <x:v>DATA-HCDN-00103</x:v>
       </x:c>
       <x:c r="I103" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J103" s="11" t="str">
         <x:v>SRC-HCDN-KPI-007</x:v>
@@ -3646,7 +3646,7 @@
         <x:v>DATA-HCDN-00104</x:v>
       </x:c>
       <x:c r="I104" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J104" s="11" t="str">
         <x:v>SRC-HCDN-KPI-008</x:v>
@@ -3663,7 +3663,7 @@
         <x:v>Imaging</x:v>
       </x:c>
       <x:c r="D105" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E105" s="11" t="str">
         <x:v>withheld</x:v>
@@ -3678,7 +3678,7 @@
         <x:v>DATA-HCDN-00105</x:v>
       </x:c>
       <x:c r="I105" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J105" s="11" t="str">
         <x:v>SRC-HCDN-KPI-009</x:v>
@@ -3695,7 +3695,7 @@
         <x:v>Lab</x:v>
       </x:c>
       <x:c r="D106" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E106" s="11" t="str">
         <x:v>exact</x:v>
@@ -3710,7 +3710,7 @@
         <x:v>DATA-HCDN-00106</x:v>
       </x:c>
       <x:c r="I106" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J106" s="11" t="str">
         <x:v>SRC-HCDN-KPI-010</x:v>
@@ -3742,7 +3742,7 @@
         <x:v>DATA-HCDN-00107</x:v>
       </x:c>
       <x:c r="I107" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J107" s="11" t="str">
         <x:v>SRC-HCDN-KPI-011</x:v>
@@ -3774,7 +3774,7 @@
         <x:v>DATA-HCDN-00108</x:v>
       </x:c>
       <x:c r="I108" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J108" s="11" t="str">
         <x:v>SRC-HCDN-KPI-012</x:v>
@@ -3806,7 +3806,7 @@
         <x:v>DATA-HCDN-00109</x:v>
       </x:c>
       <x:c r="I109" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J109" s="11" t="str">
         <x:v>SRC-HCDN-KPI-013</x:v>
@@ -3838,7 +3838,7 @@
         <x:v>DATA-HCDN-00110</x:v>
       </x:c>
       <x:c r="I110" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J110" s="11" t="str">
         <x:v>SRC-HCDN-KPI-014</x:v>
@@ -3870,7 +3870,7 @@
         <x:v>DATA-HCDN-00111</x:v>
       </x:c>
       <x:c r="I111" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J111" s="11" t="str">
         <x:v>SRC-HCDN-KPI-015</x:v>
@@ -3902,7 +3902,7 @@
         <x:v>DATA-HCDN-00112</x:v>
       </x:c>
       <x:c r="I112" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J112" s="11" t="str">
         <x:v>SRC-HCDN-KPI-016</x:v>
@@ -3919,7 +3919,7 @@
         <x:v>Departmental Reporting</x:v>
       </x:c>
       <x:c r="D113" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E113" s="11" t="str">
         <x:v>indexed</x:v>
@@ -3934,7 +3934,7 @@
         <x:v>DATA-HCDN-00113</x:v>
       </x:c>
       <x:c r="I113" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J113" s="11" t="str">
         <x:v>SRC-HCDN-KPI-017</x:v>
@@ -3951,7 +3951,7 @@
         <x:v>AI Transformation</x:v>
       </x:c>
       <x:c r="D114" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E114" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -3966,7 +3966,7 @@
         <x:v>DATA-HCDN-00114</x:v>
       </x:c>
       <x:c r="I114" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J114" s="11" t="str">
         <x:v>SRC-HCDN-KPI-018</x:v>
@@ -3998,7 +3998,7 @@
         <x:v>DATA-HCDN-00115</x:v>
       </x:c>
       <x:c r="I115" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J115" s="11" t="str">
         <x:v>SRC-HCDN-KPI-019</x:v>
@@ -4030,7 +4030,7 @@
         <x:v>DATA-HCDN-00116</x:v>
       </x:c>
       <x:c r="I116" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J116" s="11" t="str">
         <x:v>SRC-HCDN-KPI-020</x:v>
@@ -4062,7 +4062,7 @@
         <x:v>DATA-HCDN-00117</x:v>
       </x:c>
       <x:c r="I117" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J117" s="11" t="str">
         <x:v>SRC-HCDN-KPI-021</x:v>
@@ -4094,7 +4094,7 @@
         <x:v>DATA-HCDN-00118</x:v>
       </x:c>
       <x:c r="I118" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J118" s="11" t="str">
         <x:v>SRC-HCDN-KPI-022</x:v>
@@ -4126,7 +4126,7 @@
         <x:v>DATA-HCDN-00119</x:v>
       </x:c>
       <x:c r="I119" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J119" s="11" t="str">
         <x:v>SRC-HCDN-KPI-023</x:v>
@@ -4158,7 +4158,7 @@
         <x:v>DATA-HCDN-00120</x:v>
       </x:c>
       <x:c r="I120" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J120" s="11" t="str">
         <x:v>SRC-HCDN-KPI-024</x:v>
@@ -4175,7 +4175,7 @@
         <x:v>Compliance</x:v>
       </x:c>
       <x:c r="D121" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E121" s="11" t="str">
         <x:v>exact</x:v>
@@ -4190,7 +4190,7 @@
         <x:v>DATA-HCDN-00121</x:v>
       </x:c>
       <x:c r="I121" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J121" s="11" t="str">
         <x:v>SRC-HCDN-KPI-025</x:v>
@@ -4207,7 +4207,7 @@
         <x:v>Provider Network</x:v>
       </x:c>
       <x:c r="D122" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E122" s="11" t="str">
         <x:v>range</x:v>
@@ -4222,7 +4222,7 @@
         <x:v>DATA-HCDN-00122</x:v>
       </x:c>
       <x:c r="I122" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J122" s="11" t="str">
         <x:v>SRC-HCDN-KPI-026</x:v>
@@ -4254,7 +4254,7 @@
         <x:v>DATA-HCDN-00123</x:v>
       </x:c>
       <x:c r="I123" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J123" s="11" t="str">
         <x:v>SRC-HCDN-KPI-027</x:v>
@@ -4286,7 +4286,7 @@
         <x:v>DATA-HCDN-00124</x:v>
       </x:c>
       <x:c r="I124" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J124" s="11" t="str">
         <x:v>SRC-HCDN-KPI-028</x:v>
@@ -4318,7 +4318,7 @@
         <x:v>DATA-HCDN-00125</x:v>
       </x:c>
       <x:c r="I125" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J125" s="11" t="str">
         <x:v>SRC-HCDN-KPI-029</x:v>
@@ -4350,7 +4350,7 @@
         <x:v>DATA-HCDN-00126</x:v>
       </x:c>
       <x:c r="I126" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J126" s="11" t="str">
         <x:v>SRC-HCDN-KPI-030</x:v>
@@ -4431,7 +4431,7 @@
         <x:v>Health Plan Operations</x:v>
       </x:c>
       <x:c r="D129" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E129" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -4457,13 +4457,13 @@
         <x:v>KPI-HCDN-0129</x:v>
       </x:c>
       <x:c r="B130" s="11" t="str">
-        <x:v>Medication adherence measure 0129</x:v>
+        <x:v>HEDIS medication adherence measure 0129</x:v>
       </x:c>
       <x:c r="C130" s="11" t="str">
         <x:v>Medicare Advantage</x:v>
       </x:c>
       <x:c r="D130" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E130" s="11" t="str">
         <x:v>withheld</x:v>
@@ -4489,7 +4489,7 @@
         <x:v>KPI-HCDN-0130</x:v>
       </x:c>
       <x:c r="B131" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0130</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0130</x:v>
       </x:c>
       <x:c r="C131" s="11" t="str">
         <x:v>Claims Operations</x:v>
@@ -4521,7 +4521,7 @@
         <x:v>KPI-HCDN-0131</x:v>
       </x:c>
       <x:c r="B132" s="11" t="str">
-        <x:v>Breast cancer screening measure 0131</x:v>
+        <x:v>HEDIS breast cancer screening measure 0131</x:v>
       </x:c>
       <x:c r="C132" s="11" t="str">
         <x:v>Utilization Management</x:v>
@@ -4574,7 +4574,7 @@
         <x:v>DATA-HCDN-00133</x:v>
       </x:c>
       <x:c r="I133" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J133" s="11" t="str">
         <x:v>SRC-HCDN-KPI-037</x:v>
@@ -4606,7 +4606,7 @@
         <x:v>DATA-HCDN-00134</x:v>
       </x:c>
       <x:c r="I134" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J134" s="11" t="str">
         <x:v>SRC-HCDN-KPI-038</x:v>
@@ -4638,7 +4638,7 @@
         <x:v>DATA-HCDN-00135</x:v>
       </x:c>
       <x:c r="I135" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J135" s="11" t="str">
         <x:v>SRC-HCDN-KPI-039</x:v>
@@ -4670,7 +4670,7 @@
         <x:v>DATA-HCDN-00136</x:v>
       </x:c>
       <x:c r="I136" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J136" s="11" t="str">
         <x:v>SRC-HCDN-KPI-040</x:v>
@@ -4687,7 +4687,7 @@
         <x:v>Finance</x:v>
       </x:c>
       <x:c r="D137" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E137" s="11" t="str">
         <x:v>range</x:v>
@@ -4702,7 +4702,7 @@
         <x:v>DATA-HCDN-00137</x:v>
       </x:c>
       <x:c r="I137" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J137" s="11" t="str">
         <x:v>SRC-HCDN-KPI-041</x:v>
@@ -4719,7 +4719,7 @@
         <x:v>Coding</x:v>
       </x:c>
       <x:c r="D138" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E138" s="11" t="str">
         <x:v>indexed</x:v>
@@ -4734,7 +4734,7 @@
         <x:v>DATA-HCDN-00138</x:v>
       </x:c>
       <x:c r="I138" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J138" s="11" t="str">
         <x:v>SRC-HCDN-KPI-042</x:v>
@@ -4766,7 +4766,7 @@
         <x:v>DATA-HCDN-00139</x:v>
       </x:c>
       <x:c r="I139" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J139" s="11" t="str">
         <x:v>SRC-HCDN-KPI-043</x:v>
@@ -4798,7 +4798,7 @@
         <x:v>DATA-HCDN-00140</x:v>
       </x:c>
       <x:c r="I140" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J140" s="11" t="str">
         <x:v>SRC-HCDN-KPI-044</x:v>
@@ -4830,7 +4830,7 @@
         <x:v>DATA-HCDN-00141</x:v>
       </x:c>
       <x:c r="I141" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J141" s="11" t="str">
         <x:v>SRC-HCDN-KPI-045</x:v>
@@ -4862,7 +4862,7 @@
         <x:v>DATA-HCDN-00142</x:v>
       </x:c>
       <x:c r="I142" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J142" s="11" t="str">
         <x:v>SRC-HCDN-KPI-046</x:v>
@@ -4894,7 +4894,7 @@
         <x:v>DATA-HCDN-00143</x:v>
       </x:c>
       <x:c r="I143" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J143" s="11" t="str">
         <x:v>SRC-HCDN-KPI-047</x:v>
@@ -4926,7 +4926,7 @@
         <x:v>DATA-HCDN-00144</x:v>
       </x:c>
       <x:c r="I144" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J144" s="11" t="str">
         <x:v>SRC-HCDN-KPI-048</x:v>
@@ -4943,7 +4943,7 @@
         <x:v>Surgery</x:v>
       </x:c>
       <x:c r="D145" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E145" s="11" t="str">
         <x:v>withheld</x:v>
@@ -4958,7 +4958,7 @@
         <x:v>DATA-HCDN-00145</x:v>
       </x:c>
       <x:c r="I145" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J145" s="11" t="str">
         <x:v>SRC-HCDN-KPI-049</x:v>
@@ -4975,7 +4975,7 @@
         <x:v>Imaging</x:v>
       </x:c>
       <x:c r="D146" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E146" s="11" t="str">
         <x:v>exact</x:v>
@@ -4990,7 +4990,7 @@
         <x:v>DATA-HCDN-00146</x:v>
       </x:c>
       <x:c r="I146" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J146" s="11" t="str">
         <x:v>SRC-HCDN-KPI-050</x:v>
@@ -5022,7 +5022,7 @@
         <x:v>DATA-HCDN-00147</x:v>
       </x:c>
       <x:c r="I147" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J147" s="11" t="str">
         <x:v>SRC-HCDN-KPI-051</x:v>
@@ -5054,7 +5054,7 @@
         <x:v>DATA-HCDN-00148</x:v>
       </x:c>
       <x:c r="I148" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J148" s="11" t="str">
         <x:v>SRC-HCDN-KPI-052</x:v>
@@ -5086,7 +5086,7 @@
         <x:v>DATA-HCDN-00149</x:v>
       </x:c>
       <x:c r="I149" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J149" s="11" t="str">
         <x:v>SRC-HCDN-KPI-053</x:v>
@@ -5118,7 +5118,7 @@
         <x:v>DATA-HCDN-00150</x:v>
       </x:c>
       <x:c r="I150" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J150" s="11" t="str">
         <x:v>SRC-HCDN-KPI-054</x:v>
@@ -5150,7 +5150,7 @@
         <x:v>DATA-HCDN-00151</x:v>
       </x:c>
       <x:c r="I151" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J151" s="11" t="str">
         <x:v>SRC-HCDN-KPI-055</x:v>
@@ -5182,7 +5182,7 @@
         <x:v>DATA-HCDN-00152</x:v>
       </x:c>
       <x:c r="I152" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J152" s="11" t="str">
         <x:v>SRC-HCDN-KPI-056</x:v>
@@ -5199,7 +5199,7 @@
         <x:v>Actuarial</x:v>
       </x:c>
       <x:c r="D153" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E153" s="11" t="str">
         <x:v>indexed</x:v>
@@ -5214,7 +5214,7 @@
         <x:v>DATA-HCDN-00153</x:v>
       </x:c>
       <x:c r="I153" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J153" s="11" t="str">
         <x:v>SRC-HCDN-KPI-057</x:v>
@@ -5231,7 +5231,7 @@
         <x:v>Departmental Reporting</x:v>
       </x:c>
       <x:c r="D154" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E154" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -5246,7 +5246,7 @@
         <x:v>DATA-HCDN-00154</x:v>
       </x:c>
       <x:c r="I154" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J154" s="11" t="str">
         <x:v>SRC-HCDN-KPI-058</x:v>
@@ -5278,7 +5278,7 @@
         <x:v>DATA-HCDN-00155</x:v>
       </x:c>
       <x:c r="I155" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J155" s="11" t="str">
         <x:v>SRC-HCDN-KPI-059</x:v>
@@ -5310,7 +5310,7 @@
         <x:v>DATA-HCDN-00156</x:v>
       </x:c>
       <x:c r="I156" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J156" s="11" t="str">
         <x:v>SRC-HCDN-KPI-060</x:v>
@@ -5342,7 +5342,7 @@
         <x:v>DATA-HCDN-00157</x:v>
       </x:c>
       <x:c r="I157" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J157" s="11" t="str">
         <x:v>SRC-HCDN-KPI-061</x:v>
@@ -5374,7 +5374,7 @@
         <x:v>DATA-HCDN-00158</x:v>
       </x:c>
       <x:c r="I158" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J158" s="11" t="str">
         <x:v>SRC-HCDN-KPI-062</x:v>
@@ -5406,7 +5406,7 @@
         <x:v>DATA-HCDN-00159</x:v>
       </x:c>
       <x:c r="I159" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J159" s="11" t="str">
         <x:v>SRC-HCDN-KPI-063</x:v>
@@ -5438,7 +5438,7 @@
         <x:v>DATA-HCDN-00160</x:v>
       </x:c>
       <x:c r="I160" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J160" s="11" t="str">
         <x:v>SRC-HCDN-KPI-064</x:v>
@@ -5455,7 +5455,7 @@
         <x:v>Privacy</x:v>
       </x:c>
       <x:c r="D161" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E161" s="11" t="str">
         <x:v>exact</x:v>
@@ -5470,7 +5470,7 @@
         <x:v>DATA-HCDN-00161</x:v>
       </x:c>
       <x:c r="I161" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J161" s="11" t="str">
         <x:v>SRC-HCDN-KPI-065</x:v>
@@ -5481,13 +5481,13 @@
         <x:v>KPI-HCDN-0161</x:v>
       </x:c>
       <x:c r="B162" s="11" t="str">
-        <x:v>Medication adherence measure 0161</x:v>
+        <x:v>HEDIS medication adherence measure 0161</x:v>
       </x:c>
       <x:c r="C162" s="11" t="str">
         <x:v>Compliance</x:v>
       </x:c>
       <x:c r="D162" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E162" s="11" t="str">
         <x:v>range</x:v>
@@ -5502,7 +5502,7 @@
         <x:v>DATA-HCDN-00162</x:v>
       </x:c>
       <x:c r="I162" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J162" s="11" t="str">
         <x:v>SRC-HCDN-KPI-066</x:v>
@@ -5513,7 +5513,7 @@
         <x:v>KPI-HCDN-0162</x:v>
       </x:c>
       <x:c r="B163" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0162</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0162</x:v>
       </x:c>
       <x:c r="C163" s="11" t="str">
         <x:v>Provider Network</x:v>
@@ -5534,7 +5534,7 @@
         <x:v>DATA-HCDN-00163</x:v>
       </x:c>
       <x:c r="I163" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J163" s="11" t="str">
         <x:v>SRC-HCDN-KPI-067</x:v>
@@ -5545,7 +5545,7 @@
         <x:v>KPI-HCDN-0163</x:v>
       </x:c>
       <x:c r="B164" s="11" t="str">
-        <x:v>Breast cancer screening measure 0163</x:v>
+        <x:v>HEDIS breast cancer screening measure 0163</x:v>
       </x:c>
       <x:c r="C164" s="11" t="str">
         <x:v>Value-Based Care</x:v>
@@ -5566,7 +5566,7 @@
         <x:v>DATA-HCDN-00164</x:v>
       </x:c>
       <x:c r="I164" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J164" s="11" t="str">
         <x:v>SRC-HCDN-KPI-068</x:v>
@@ -5598,7 +5598,7 @@
         <x:v>DATA-HCDN-00165</x:v>
       </x:c>
       <x:c r="I165" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J165" s="11" t="str">
         <x:v>SRC-HCDN-KPI-069</x:v>
@@ -5630,7 +5630,7 @@
         <x:v>DATA-HCDN-00166</x:v>
       </x:c>
       <x:c r="I166" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J166" s="11" t="str">
         <x:v>SRC-HCDN-KPI-070</x:v>
@@ -5662,7 +5662,7 @@
         <x:v>DATA-HCDN-00167</x:v>
       </x:c>
       <x:c r="I167" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J167" s="11" t="str">
         <x:v>SRC-HCDN-KPI-071</x:v>
@@ -5694,7 +5694,7 @@
         <x:v>DATA-HCDN-00168</x:v>
       </x:c>
       <x:c r="I168" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J168" s="11" t="str">
         <x:v>SRC-HCDN-KPI-072</x:v>
@@ -5711,7 +5711,7 @@
         <x:v>Population Health</x:v>
       </x:c>
       <x:c r="D169" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E169" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -5743,7 +5743,7 @@
         <x:v>Health Plan Operations</x:v>
       </x:c>
       <x:c r="D170" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E170" s="11" t="str">
         <x:v>withheld</x:v>
@@ -5918,7 +5918,7 @@
         <x:v>DATA-HCDN-00175</x:v>
       </x:c>
       <x:c r="I175" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J175" s="11" t="str">
         <x:v>SRC-HCDN-KPI-079</x:v>
@@ -5950,7 +5950,7 @@
         <x:v>DATA-HCDN-00176</x:v>
       </x:c>
       <x:c r="I176" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J176" s="11" t="str">
         <x:v>SRC-HCDN-KPI-080</x:v>
@@ -5967,7 +5967,7 @@
         <x:v>Care Management</x:v>
       </x:c>
       <x:c r="D177" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E177" s="11" t="str">
         <x:v>range</x:v>
@@ -5982,7 +5982,7 @@
         <x:v>DATA-HCDN-00177</x:v>
       </x:c>
       <x:c r="I177" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J177" s="11" t="str">
         <x:v>SRC-HCDN-KPI-081</x:v>
@@ -5999,7 +5999,7 @@
         <x:v>Finance</x:v>
       </x:c>
       <x:c r="D178" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E178" s="11" t="str">
         <x:v>indexed</x:v>
@@ -6014,7 +6014,7 @@
         <x:v>DATA-HCDN-00178</x:v>
       </x:c>
       <x:c r="I178" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J178" s="11" t="str">
         <x:v>SRC-HCDN-KPI-082</x:v>
@@ -6046,7 +6046,7 @@
         <x:v>DATA-HCDN-00179</x:v>
       </x:c>
       <x:c r="I179" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J179" s="11" t="str">
         <x:v>SRC-HCDN-KPI-083</x:v>
@@ -6078,7 +6078,7 @@
         <x:v>DATA-HCDN-00180</x:v>
       </x:c>
       <x:c r="I180" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J180" s="11" t="str">
         <x:v>SRC-HCDN-KPI-084</x:v>
@@ -6110,7 +6110,7 @@
         <x:v>DATA-HCDN-00181</x:v>
       </x:c>
       <x:c r="I181" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J181" s="11" t="str">
         <x:v>SRC-HCDN-KPI-085</x:v>
@@ -6142,7 +6142,7 @@
         <x:v>DATA-HCDN-00182</x:v>
       </x:c>
       <x:c r="I182" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J182" s="11" t="str">
         <x:v>SRC-HCDN-KPI-086</x:v>
@@ -6174,7 +6174,7 @@
         <x:v>DATA-HCDN-00183</x:v>
       </x:c>
       <x:c r="I183" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J183" s="11" t="str">
         <x:v>SRC-HCDN-KPI-087</x:v>
@@ -6206,7 +6206,7 @@
         <x:v>DATA-HCDN-00184</x:v>
       </x:c>
       <x:c r="I184" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J184" s="11" t="str">
         <x:v>SRC-HCDN-KPI-088</x:v>
@@ -6223,7 +6223,7 @@
         <x:v>Inpatient</x:v>
       </x:c>
       <x:c r="D185" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E185" s="11" t="str">
         <x:v>withheld</x:v>
@@ -6238,7 +6238,7 @@
         <x:v>DATA-HCDN-00185</x:v>
       </x:c>
       <x:c r="I185" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J185" s="11" t="str">
         <x:v>SRC-HCDN-KPI-089</x:v>
@@ -6255,7 +6255,7 @@
         <x:v>Surgery</x:v>
       </x:c>
       <x:c r="D186" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E186" s="11" t="str">
         <x:v>exact</x:v>
@@ -6270,7 +6270,7 @@
         <x:v>DATA-HCDN-00186</x:v>
       </x:c>
       <x:c r="I186" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J186" s="11" t="str">
         <x:v>SRC-HCDN-KPI-090</x:v>
@@ -6302,7 +6302,7 @@
         <x:v>DATA-HCDN-00187</x:v>
       </x:c>
       <x:c r="I187" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J187" s="11" t="str">
         <x:v>SRC-HCDN-KPI-091</x:v>
@@ -6334,7 +6334,7 @@
         <x:v>DATA-HCDN-00188</x:v>
       </x:c>
       <x:c r="I188" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J188" s="11" t="str">
         <x:v>SRC-HCDN-KPI-092</x:v>
@@ -6366,7 +6366,7 @@
         <x:v>DATA-HCDN-00189</x:v>
       </x:c>
       <x:c r="I189" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J189" s="11" t="str">
         <x:v>SRC-HCDN-KPI-093</x:v>
@@ -6398,7 +6398,7 @@
         <x:v>DATA-HCDN-00190</x:v>
       </x:c>
       <x:c r="I190" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J190" s="11" t="str">
         <x:v>SRC-HCDN-KPI-094</x:v>
@@ -6430,7 +6430,7 @@
         <x:v>DATA-HCDN-00191</x:v>
       </x:c>
       <x:c r="I191" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J191" s="11" t="str">
         <x:v>SRC-HCDN-KPI-095</x:v>
@@ -6462,7 +6462,7 @@
         <x:v>DATA-HCDN-00192</x:v>
       </x:c>
       <x:c r="I192" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J192" s="11" t="str">
         <x:v>SRC-HCDN-KPI-096</x:v>
@@ -6479,7 +6479,7 @@
         <x:v>Clinical Analytics</x:v>
       </x:c>
       <x:c r="D193" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E193" s="11" t="str">
         <x:v>indexed</x:v>
@@ -6494,7 +6494,7 @@
         <x:v>DATA-HCDN-00193</x:v>
       </x:c>
       <x:c r="I193" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J193" s="11" t="str">
         <x:v>SRC-HCDN-KPI-001</x:v>
@@ -6505,13 +6505,13 @@
         <x:v>KPI-HCDN-0193</x:v>
       </x:c>
       <x:c r="B194" s="11" t="str">
-        <x:v>Medication adherence measure 0193</x:v>
+        <x:v>HEDIS medication adherence measure 0193</x:v>
       </x:c>
       <x:c r="C194" s="11" t="str">
         <x:v>Actuarial</x:v>
       </x:c>
       <x:c r="D194" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E194" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -6526,7 +6526,7 @@
         <x:v>DATA-HCDN-00194</x:v>
       </x:c>
       <x:c r="I194" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J194" s="11" t="str">
         <x:v>SRC-HCDN-KPI-002</x:v>
@@ -6537,7 +6537,7 @@
         <x:v>KPI-HCDN-0194</x:v>
       </x:c>
       <x:c r="B195" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0194</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0194</x:v>
       </x:c>
       <x:c r="C195" s="11" t="str">
         <x:v>Departmental Reporting</x:v>
@@ -6558,7 +6558,7 @@
         <x:v>DATA-HCDN-00195</x:v>
       </x:c>
       <x:c r="I195" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J195" s="11" t="str">
         <x:v>SRC-HCDN-KPI-003</x:v>
@@ -6569,7 +6569,7 @@
         <x:v>KPI-HCDN-0195</x:v>
       </x:c>
       <x:c r="B196" s="11" t="str">
-        <x:v>Breast cancer screening measure 0195</x:v>
+        <x:v>HEDIS breast cancer screening measure 0195</x:v>
       </x:c>
       <x:c r="C196" s="11" t="str">
         <x:v>AI Transformation</x:v>
@@ -6590,7 +6590,7 @@
         <x:v>DATA-HCDN-00196</x:v>
       </x:c>
       <x:c r="I196" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J196" s="11" t="str">
         <x:v>SRC-HCDN-KPI-004</x:v>
@@ -6622,7 +6622,7 @@
         <x:v>DATA-HCDN-00197</x:v>
       </x:c>
       <x:c r="I197" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J197" s="11" t="str">
         <x:v>SRC-HCDN-KPI-005</x:v>
@@ -6654,7 +6654,7 @@
         <x:v>DATA-HCDN-00198</x:v>
       </x:c>
       <x:c r="I198" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J198" s="11" t="str">
         <x:v>SRC-HCDN-KPI-006</x:v>
@@ -6686,7 +6686,7 @@
         <x:v>DATA-HCDN-00199</x:v>
       </x:c>
       <x:c r="I199" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J199" s="11" t="str">
         <x:v>SRC-HCDN-KPI-007</x:v>
@@ -6718,7 +6718,7 @@
         <x:v>DATA-HCDN-00200</x:v>
       </x:c>
       <x:c r="I200" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J200" s="11" t="str">
         <x:v>SRC-HCDN-KPI-008</x:v>
@@ -6735,7 +6735,7 @@
         <x:v>Supply Chain</x:v>
       </x:c>
       <x:c r="D201" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E201" s="11" t="str">
         <x:v>exact</x:v>
@@ -6750,7 +6750,7 @@
         <x:v>DATA-HCDN-00201</x:v>
       </x:c>
       <x:c r="I201" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J201" s="11" t="str">
         <x:v>SRC-HCDN-KPI-009</x:v>
@@ -6767,7 +6767,7 @@
         <x:v>Privacy</x:v>
       </x:c>
       <x:c r="D202" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E202" s="11" t="str">
         <x:v>range</x:v>
@@ -6782,7 +6782,7 @@
         <x:v>DATA-HCDN-00202</x:v>
       </x:c>
       <x:c r="I202" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J202" s="11" t="str">
         <x:v>SRC-HCDN-KPI-010</x:v>
@@ -6814,7 +6814,7 @@
         <x:v>DATA-HCDN-00203</x:v>
       </x:c>
       <x:c r="I203" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J203" s="11" t="str">
         <x:v>SRC-HCDN-KPI-011</x:v>
@@ -6846,7 +6846,7 @@
         <x:v>DATA-HCDN-00204</x:v>
       </x:c>
       <x:c r="I204" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J204" s="11" t="str">
         <x:v>SRC-HCDN-KPI-012</x:v>
@@ -6878,7 +6878,7 @@
         <x:v>DATA-HCDN-00205</x:v>
       </x:c>
       <x:c r="I205" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J205" s="11" t="str">
         <x:v>SRC-HCDN-KPI-013</x:v>
@@ -6910,7 +6910,7 @@
         <x:v>DATA-HCDN-00206</x:v>
       </x:c>
       <x:c r="I206" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J206" s="11" t="str">
         <x:v>SRC-HCDN-KPI-014</x:v>
@@ -6942,7 +6942,7 @@
         <x:v>DATA-HCDN-00207</x:v>
       </x:c>
       <x:c r="I207" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J207" s="11" t="str">
         <x:v>SRC-HCDN-KPI-015</x:v>
@@ -6974,7 +6974,7 @@
         <x:v>DATA-HCDN-00208</x:v>
       </x:c>
       <x:c r="I208" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J208" s="11" t="str">
         <x:v>SRC-HCDN-KPI-016</x:v>
@@ -6991,7 +6991,7 @@
         <x:v>Interoperability</x:v>
       </x:c>
       <x:c r="D209" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E209" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -7006,7 +7006,7 @@
         <x:v>DATA-HCDN-00209</x:v>
       </x:c>
       <x:c r="I209" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J209" s="11" t="str">
         <x:v>SRC-HCDN-KPI-017</x:v>
@@ -7023,7 +7023,7 @@
         <x:v>Population Health</x:v>
       </x:c>
       <x:c r="D210" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E210" s="11" t="str">
         <x:v>withheld</x:v>
@@ -7038,7 +7038,7 @@
         <x:v>DATA-HCDN-00210</x:v>
       </x:c>
       <x:c r="I210" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J210" s="11" t="str">
         <x:v>SRC-HCDN-KPI-018</x:v>
@@ -7247,7 +7247,7 @@
         <x:v>Risk Adjustment</x:v>
       </x:c>
       <x:c r="D217" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E217" s="11" t="str">
         <x:v>range</x:v>
@@ -7262,7 +7262,7 @@
         <x:v>DATA-HCDN-00217</x:v>
       </x:c>
       <x:c r="I217" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J217" s="11" t="str">
         <x:v>SRC-HCDN-KPI-025</x:v>
@@ -7279,7 +7279,7 @@
         <x:v>Care Management</x:v>
       </x:c>
       <x:c r="D218" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E218" s="11" t="str">
         <x:v>indexed</x:v>
@@ -7294,7 +7294,7 @@
         <x:v>DATA-HCDN-00218</x:v>
       </x:c>
       <x:c r="I218" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J218" s="11" t="str">
         <x:v>SRC-HCDN-KPI-026</x:v>
@@ -7326,7 +7326,7 @@
         <x:v>DATA-HCDN-00219</x:v>
       </x:c>
       <x:c r="I219" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J219" s="11" t="str">
         <x:v>SRC-HCDN-KPI-027</x:v>
@@ -7358,7 +7358,7 @@
         <x:v>DATA-HCDN-00220</x:v>
       </x:c>
       <x:c r="I220" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J220" s="11" t="str">
         <x:v>SRC-HCDN-KPI-028</x:v>
@@ -7390,7 +7390,7 @@
         <x:v>DATA-HCDN-00221</x:v>
       </x:c>
       <x:c r="I221" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J221" s="11" t="str">
         <x:v>SRC-HCDN-KPI-029</x:v>
@@ -7422,7 +7422,7 @@
         <x:v>DATA-HCDN-00222</x:v>
       </x:c>
       <x:c r="I222" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J222" s="11" t="str">
         <x:v>SRC-HCDN-KPI-030</x:v>
@@ -7454,7 +7454,7 @@
         <x:v>DATA-HCDN-00223</x:v>
       </x:c>
       <x:c r="I223" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J223" s="11" t="str">
         <x:v>SRC-HCDN-KPI-031</x:v>
@@ -7486,7 +7486,7 @@
         <x:v>DATA-HCDN-00224</x:v>
       </x:c>
       <x:c r="I224" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J224" s="11" t="str">
         <x:v>SRC-HCDN-KPI-032</x:v>
@@ -7503,7 +7503,7 @@
         <x:v>Emergency Department</x:v>
       </x:c>
       <x:c r="D225" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E225" s="11" t="str">
         <x:v>withheld</x:v>
@@ -7518,7 +7518,7 @@
         <x:v>DATA-HCDN-00225</x:v>
       </x:c>
       <x:c r="I225" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J225" s="11" t="str">
         <x:v>SRC-HCDN-KPI-033</x:v>
@@ -7529,13 +7529,13 @@
         <x:v>KPI-HCDN-0225</x:v>
       </x:c>
       <x:c r="B226" s="11" t="str">
-        <x:v>Medication adherence measure 0225</x:v>
+        <x:v>HEDIS medication adherence measure 0225</x:v>
       </x:c>
       <x:c r="C226" s="11" t="str">
         <x:v>Inpatient</x:v>
       </x:c>
       <x:c r="D226" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E226" s="11" t="str">
         <x:v>exact</x:v>
@@ -7550,7 +7550,7 @@
         <x:v>DATA-HCDN-00226</x:v>
       </x:c>
       <x:c r="I226" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J226" s="11" t="str">
         <x:v>SRC-HCDN-KPI-034</x:v>
@@ -7561,7 +7561,7 @@
         <x:v>KPI-HCDN-0226</x:v>
       </x:c>
       <x:c r="B227" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0226</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0226</x:v>
       </x:c>
       <x:c r="C227" s="11" t="str">
         <x:v>Surgery</x:v>
@@ -7582,7 +7582,7 @@
         <x:v>DATA-HCDN-00227</x:v>
       </x:c>
       <x:c r="I227" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J227" s="11" t="str">
         <x:v>SRC-HCDN-KPI-035</x:v>
@@ -7593,7 +7593,7 @@
         <x:v>KPI-HCDN-0227</x:v>
       </x:c>
       <x:c r="B228" s="11" t="str">
-        <x:v>Breast cancer screening measure 0227</x:v>
+        <x:v>HEDIS breast cancer screening measure 0227</x:v>
       </x:c>
       <x:c r="C228" s="11" t="str">
         <x:v>Imaging</x:v>
@@ -7614,7 +7614,7 @@
         <x:v>DATA-HCDN-00228</x:v>
       </x:c>
       <x:c r="I228" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J228" s="11" t="str">
         <x:v>SRC-HCDN-KPI-036</x:v>
@@ -7646,7 +7646,7 @@
         <x:v>DATA-HCDN-00229</x:v>
       </x:c>
       <x:c r="I229" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J229" s="11" t="str">
         <x:v>SRC-HCDN-KPI-037</x:v>
@@ -7678,7 +7678,7 @@
         <x:v>DATA-HCDN-00230</x:v>
       </x:c>
       <x:c r="I230" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J230" s="11" t="str">
         <x:v>SRC-HCDN-KPI-038</x:v>
@@ -7710,7 +7710,7 @@
         <x:v>DATA-HCDN-00231</x:v>
       </x:c>
       <x:c r="I231" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J231" s="11" t="str">
         <x:v>SRC-HCDN-KPI-039</x:v>
@@ -7742,7 +7742,7 @@
         <x:v>DATA-HCDN-00232</x:v>
       </x:c>
       <x:c r="I232" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J232" s="11" t="str">
         <x:v>SRC-HCDN-KPI-040</x:v>
@@ -7759,7 +7759,7 @@
         <x:v>Data and Analytics</x:v>
       </x:c>
       <x:c r="D233" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E233" s="11" t="str">
         <x:v>indexed</x:v>
@@ -7774,7 +7774,7 @@
         <x:v>DATA-HCDN-00233</x:v>
       </x:c>
       <x:c r="I233" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J233" s="11" t="str">
         <x:v>SRC-HCDN-KPI-041</x:v>
@@ -7791,7 +7791,7 @@
         <x:v>Clinical Analytics</x:v>
       </x:c>
       <x:c r="D234" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E234" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -7806,7 +7806,7 @@
         <x:v>DATA-HCDN-00234</x:v>
       </x:c>
       <x:c r="I234" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J234" s="11" t="str">
         <x:v>SRC-HCDN-KPI-042</x:v>
@@ -7838,7 +7838,7 @@
         <x:v>DATA-HCDN-00235</x:v>
       </x:c>
       <x:c r="I235" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J235" s="11" t="str">
         <x:v>SRC-HCDN-KPI-043</x:v>
@@ -7870,7 +7870,7 @@
         <x:v>DATA-HCDN-00236</x:v>
       </x:c>
       <x:c r="I236" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J236" s="11" t="str">
         <x:v>SRC-HCDN-KPI-044</x:v>
@@ -7902,7 +7902,7 @@
         <x:v>DATA-HCDN-00237</x:v>
       </x:c>
       <x:c r="I237" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J237" s="11" t="str">
         <x:v>SRC-HCDN-KPI-045</x:v>
@@ -7934,7 +7934,7 @@
         <x:v>DATA-HCDN-00238</x:v>
       </x:c>
       <x:c r="I238" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J238" s="11" t="str">
         <x:v>SRC-HCDN-KPI-046</x:v>
@@ -7966,7 +7966,7 @@
         <x:v>DATA-HCDN-00239</x:v>
       </x:c>
       <x:c r="I239" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J239" s="11" t="str">
         <x:v>SRC-HCDN-KPI-047</x:v>
@@ -7998,7 +7998,7 @@
         <x:v>DATA-HCDN-00240</x:v>
       </x:c>
       <x:c r="I240" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J240" s="11" t="str">
         <x:v>SRC-HCDN-KPI-048</x:v>
@@ -8015,7 +8015,7 @@
         <x:v>HR</x:v>
       </x:c>
       <x:c r="D241" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E241" s="11" t="str">
         <x:v>exact</x:v>
@@ -8030,7 +8030,7 @@
         <x:v>DATA-HCDN-00241</x:v>
       </x:c>
       <x:c r="I241" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J241" s="11" t="str">
         <x:v>SRC-HCDN-KPI-049</x:v>
@@ -8047,7 +8047,7 @@
         <x:v>Supply Chain</x:v>
       </x:c>
       <x:c r="D242" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E242" s="11" t="str">
         <x:v>range</x:v>
@@ -8062,7 +8062,7 @@
         <x:v>DATA-HCDN-00242</x:v>
       </x:c>
       <x:c r="I242" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J242" s="11" t="str">
         <x:v>SRC-HCDN-KPI-050</x:v>
@@ -8094,7 +8094,7 @@
         <x:v>DATA-HCDN-00243</x:v>
       </x:c>
       <x:c r="I243" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J243" s="11" t="str">
         <x:v>SRC-HCDN-KPI-051</x:v>
@@ -8126,7 +8126,7 @@
         <x:v>DATA-HCDN-00244</x:v>
       </x:c>
       <x:c r="I244" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J244" s="11" t="str">
         <x:v>SRC-HCDN-KPI-052</x:v>
@@ -8158,7 +8158,7 @@
         <x:v>DATA-HCDN-00245</x:v>
       </x:c>
       <x:c r="I245" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J245" s="11" t="str">
         <x:v>SRC-HCDN-KPI-053</x:v>
@@ -8190,7 +8190,7 @@
         <x:v>DATA-HCDN-00246</x:v>
       </x:c>
       <x:c r="I246" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J246" s="11" t="str">
         <x:v>SRC-HCDN-KPI-054</x:v>
@@ -8222,7 +8222,7 @@
         <x:v>DATA-HCDN-00247</x:v>
       </x:c>
       <x:c r="I247" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J247" s="11" t="str">
         <x:v>SRC-HCDN-KPI-055</x:v>
@@ -8254,7 +8254,7 @@
         <x:v>DATA-HCDN-00248</x:v>
       </x:c>
       <x:c r="I248" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J248" s="11" t="str">
         <x:v>SRC-HCDN-KPI-056</x:v>
@@ -8271,7 +8271,7 @@
         <x:v>Patient Access</x:v>
       </x:c>
       <x:c r="D249" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E249" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -8286,7 +8286,7 @@
         <x:v>DATA-HCDN-00249</x:v>
       </x:c>
       <x:c r="I249" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J249" s="11" t="str">
         <x:v>SRC-HCDN-KPI-057</x:v>
@@ -8303,7 +8303,7 @@
         <x:v>Interoperability</x:v>
       </x:c>
       <x:c r="D250" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E250" s="11" t="str">
         <x:v>withheld</x:v>
@@ -8318,7 +8318,7 @@
         <x:v>DATA-HCDN-00250</x:v>
       </x:c>
       <x:c r="I250" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J250" s="11" t="str">
         <x:v>SRC-HCDN-KPI-058</x:v>
@@ -8350,7 +8350,7 @@
         <x:v>DATA-HCDN-00251</x:v>
       </x:c>
       <x:c r="I251" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J251" s="11" t="str">
         <x:v>SRC-HCDN-KPI-059</x:v>
@@ -8382,7 +8382,7 @@
         <x:v>DATA-HCDN-00252</x:v>
       </x:c>
       <x:c r="I252" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J252" s="11" t="str">
         <x:v>SRC-HCDN-KPI-060</x:v>
@@ -8527,7 +8527,7 @@
         <x:v>Quality and Stars</x:v>
       </x:c>
       <x:c r="D257" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E257" s="11" t="str">
         <x:v>range</x:v>
@@ -8553,13 +8553,13 @@
         <x:v>KPI-HCDN-0257</x:v>
       </x:c>
       <x:c r="B258" s="11" t="str">
-        <x:v>Medication adherence measure 0257</x:v>
+        <x:v>HEDIS medication adherence measure 0257</x:v>
       </x:c>
       <x:c r="C258" s="11" t="str">
         <x:v>Risk Adjustment</x:v>
       </x:c>
       <x:c r="D258" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E258" s="11" t="str">
         <x:v>indexed</x:v>
@@ -8585,7 +8585,7 @@
         <x:v>KPI-HCDN-0258</x:v>
       </x:c>
       <x:c r="B259" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0258</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0258</x:v>
       </x:c>
       <x:c r="C259" s="11" t="str">
         <x:v>Care Management</x:v>
@@ -8606,7 +8606,7 @@
         <x:v>DATA-HCDN-00259</x:v>
       </x:c>
       <x:c r="I259" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J259" s="11" t="str">
         <x:v>SRC-HCDN-KPI-067</x:v>
@@ -8617,7 +8617,7 @@
         <x:v>KPI-HCDN-0259</x:v>
       </x:c>
       <x:c r="B260" s="11" t="str">
-        <x:v>Breast cancer screening measure 0259</x:v>
+        <x:v>HEDIS breast cancer screening measure 0259</x:v>
       </x:c>
       <x:c r="C260" s="11" t="str">
         <x:v>Finance</x:v>
@@ -8638,7 +8638,7 @@
         <x:v>DATA-HCDN-00260</x:v>
       </x:c>
       <x:c r="I260" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J260" s="11" t="str">
         <x:v>SRC-HCDN-KPI-068</x:v>
@@ -8670,7 +8670,7 @@
         <x:v>DATA-HCDN-00261</x:v>
       </x:c>
       <x:c r="I261" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J261" s="11" t="str">
         <x:v>SRC-HCDN-KPI-069</x:v>
@@ -8702,7 +8702,7 @@
         <x:v>DATA-HCDN-00262</x:v>
       </x:c>
       <x:c r="I262" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J262" s="11" t="str">
         <x:v>SRC-HCDN-KPI-070</x:v>
@@ -8734,7 +8734,7 @@
         <x:v>DATA-HCDN-00263</x:v>
       </x:c>
       <x:c r="I263" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J263" s="11" t="str">
         <x:v>SRC-HCDN-KPI-071</x:v>
@@ -8766,7 +8766,7 @@
         <x:v>DATA-HCDN-00264</x:v>
       </x:c>
       <x:c r="I264" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J264" s="11" t="str">
         <x:v>SRC-HCDN-KPI-072</x:v>
@@ -8783,7 +8783,7 @@
         <x:v>Ambulatory Care</x:v>
       </x:c>
       <x:c r="D265" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E265" s="11" t="str">
         <x:v>withheld</x:v>
@@ -8798,7 +8798,7 @@
         <x:v>DATA-HCDN-00265</x:v>
       </x:c>
       <x:c r="I265" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J265" s="11" t="str">
         <x:v>SRC-HCDN-KPI-073</x:v>
@@ -8815,7 +8815,7 @@
         <x:v>Emergency Department</x:v>
       </x:c>
       <x:c r="D266" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E266" s="11" t="str">
         <x:v>exact</x:v>
@@ -8830,7 +8830,7 @@
         <x:v>DATA-HCDN-00266</x:v>
       </x:c>
       <x:c r="I266" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J266" s="11" t="str">
         <x:v>SRC-HCDN-KPI-074</x:v>
@@ -8862,7 +8862,7 @@
         <x:v>DATA-HCDN-00267</x:v>
       </x:c>
       <x:c r="I267" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J267" s="11" t="str">
         <x:v>SRC-HCDN-KPI-075</x:v>
@@ -8894,7 +8894,7 @@
         <x:v>DATA-HCDN-00268</x:v>
       </x:c>
       <x:c r="I268" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J268" s="11" t="str">
         <x:v>SRC-HCDN-KPI-076</x:v>
@@ -8926,7 +8926,7 @@
         <x:v>DATA-HCDN-00269</x:v>
       </x:c>
       <x:c r="I269" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J269" s="11" t="str">
         <x:v>SRC-HCDN-KPI-077</x:v>
@@ -8958,7 +8958,7 @@
         <x:v>DATA-HCDN-00270</x:v>
       </x:c>
       <x:c r="I270" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J270" s="11" t="str">
         <x:v>SRC-HCDN-KPI-078</x:v>
@@ -8990,7 +8990,7 @@
         <x:v>DATA-HCDN-00271</x:v>
       </x:c>
       <x:c r="I271" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J271" s="11" t="str">
         <x:v>SRC-HCDN-KPI-079</x:v>
@@ -9022,7 +9022,7 @@
         <x:v>DATA-HCDN-00272</x:v>
       </x:c>
       <x:c r="I272" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J272" s="11" t="str">
         <x:v>SRC-HCDN-KPI-080</x:v>
@@ -9039,7 +9039,7 @@
         <x:v>Cardiology</x:v>
       </x:c>
       <x:c r="D273" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E273" s="11" t="str">
         <x:v>indexed</x:v>
@@ -9054,7 +9054,7 @@
         <x:v>DATA-HCDN-00273</x:v>
       </x:c>
       <x:c r="I273" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J273" s="11" t="str">
         <x:v>SRC-HCDN-KPI-081</x:v>
@@ -9071,7 +9071,7 @@
         <x:v>Data and Analytics</x:v>
       </x:c>
       <x:c r="D274" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E274" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -9086,7 +9086,7 @@
         <x:v>DATA-HCDN-00274</x:v>
       </x:c>
       <x:c r="I274" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J274" s="11" t="str">
         <x:v>SRC-HCDN-KPI-082</x:v>
@@ -9118,7 +9118,7 @@
         <x:v>DATA-HCDN-00275</x:v>
       </x:c>
       <x:c r="I275" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J275" s="11" t="str">
         <x:v>SRC-HCDN-KPI-083</x:v>
@@ -9150,7 +9150,7 @@
         <x:v>DATA-HCDN-00276</x:v>
       </x:c>
       <x:c r="I276" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J276" s="11" t="str">
         <x:v>SRC-HCDN-KPI-084</x:v>
@@ -9182,7 +9182,7 @@
         <x:v>DATA-HCDN-00277</x:v>
       </x:c>
       <x:c r="I277" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J277" s="11" t="str">
         <x:v>SRC-HCDN-KPI-085</x:v>
@@ -9214,7 +9214,7 @@
         <x:v>DATA-HCDN-00278</x:v>
       </x:c>
       <x:c r="I278" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J278" s="11" t="str">
         <x:v>SRC-HCDN-KPI-086</x:v>
@@ -9246,7 +9246,7 @@
         <x:v>DATA-HCDN-00279</x:v>
       </x:c>
       <x:c r="I279" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J279" s="11" t="str">
         <x:v>SRC-HCDN-KPI-087</x:v>
@@ -9278,7 +9278,7 @@
         <x:v>DATA-HCDN-00280</x:v>
       </x:c>
       <x:c r="I280" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J280" s="11" t="str">
         <x:v>SRC-HCDN-KPI-088</x:v>
@@ -9295,7 +9295,7 @@
         <x:v>Procurement</x:v>
       </x:c>
       <x:c r="D281" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E281" s="11" t="str">
         <x:v>exact</x:v>
@@ -9310,7 +9310,7 @@
         <x:v>DATA-HCDN-00281</x:v>
       </x:c>
       <x:c r="I281" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J281" s="11" t="str">
         <x:v>SRC-HCDN-KPI-089</x:v>
@@ -9327,7 +9327,7 @@
         <x:v>HR</x:v>
       </x:c>
       <x:c r="D282" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E282" s="11" t="str">
         <x:v>range</x:v>
@@ -9342,7 +9342,7 @@
         <x:v>DATA-HCDN-00282</x:v>
       </x:c>
       <x:c r="I282" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J282" s="11" t="str">
         <x:v>SRC-HCDN-KPI-090</x:v>
@@ -9374,7 +9374,7 @@
         <x:v>DATA-HCDN-00283</x:v>
       </x:c>
       <x:c r="I283" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J283" s="11" t="str">
         <x:v>SRC-HCDN-KPI-091</x:v>
@@ -9406,7 +9406,7 @@
         <x:v>DATA-HCDN-00284</x:v>
       </x:c>
       <x:c r="I284" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J284" s="11" t="str">
         <x:v>SRC-HCDN-KPI-092</x:v>
@@ -9438,7 +9438,7 @@
         <x:v>DATA-HCDN-00285</x:v>
       </x:c>
       <x:c r="I285" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J285" s="11" t="str">
         <x:v>SRC-HCDN-KPI-093</x:v>
@@ -9470,7 +9470,7 @@
         <x:v>DATA-HCDN-00286</x:v>
       </x:c>
       <x:c r="I286" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J286" s="11" t="str">
         <x:v>SRC-HCDN-KPI-094</x:v>
@@ -9502,7 +9502,7 @@
         <x:v>DATA-HCDN-00287</x:v>
       </x:c>
       <x:c r="I287" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J287" s="11" t="str">
         <x:v>SRC-HCDN-KPI-095</x:v>
@@ -9534,7 +9534,7 @@
         <x:v>DATA-HCDN-00288</x:v>
       </x:c>
       <x:c r="I288" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J288" s="11" t="str">
         <x:v>SRC-HCDN-KPI-096</x:v>
@@ -9551,7 +9551,7 @@
         <x:v>Revenue Cycle</x:v>
       </x:c>
       <x:c r="D289" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E289" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -9566,7 +9566,7 @@
         <x:v>DATA-HCDN-00289</x:v>
       </x:c>
       <x:c r="I289" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J289" s="11" t="str">
         <x:v>SRC-HCDN-KPI-001</x:v>
@@ -9577,13 +9577,13 @@
         <x:v>KPI-HCDN-0289</x:v>
       </x:c>
       <x:c r="B290" s="11" t="str">
-        <x:v>Medication adherence measure 0289</x:v>
+        <x:v>HEDIS medication adherence measure 0289</x:v>
       </x:c>
       <x:c r="C290" s="11" t="str">
         <x:v>Patient Access</x:v>
       </x:c>
       <x:c r="D290" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E290" s="11" t="str">
         <x:v>withheld</x:v>
@@ -9598,7 +9598,7 @@
         <x:v>DATA-HCDN-00290</x:v>
       </x:c>
       <x:c r="I290" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J290" s="11" t="str">
         <x:v>SRC-HCDN-KPI-002</x:v>
@@ -9609,7 +9609,7 @@
         <x:v>KPI-HCDN-0290</x:v>
       </x:c>
       <x:c r="B291" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0290</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0290</x:v>
       </x:c>
       <x:c r="C291" s="11" t="str">
         <x:v>Interoperability</x:v>
@@ -9630,7 +9630,7 @@
         <x:v>DATA-HCDN-00291</x:v>
       </x:c>
       <x:c r="I291" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J291" s="11" t="str">
         <x:v>SRC-HCDN-KPI-003</x:v>
@@ -9641,7 +9641,7 @@
         <x:v>KPI-HCDN-0291</x:v>
       </x:c>
       <x:c r="B292" s="11" t="str">
-        <x:v>Breast cancer screening measure 0291</x:v>
+        <x:v>HEDIS breast cancer screening measure 0291</x:v>
       </x:c>
       <x:c r="C292" s="11" t="str">
         <x:v>Population Health</x:v>
@@ -9662,7 +9662,7 @@
         <x:v>DATA-HCDN-00292</x:v>
       </x:c>
       <x:c r="I292" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J292" s="11" t="str">
         <x:v>SRC-HCDN-KPI-004</x:v>
@@ -9694,7 +9694,7 @@
         <x:v>DATA-HCDN-00293</x:v>
       </x:c>
       <x:c r="I293" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J293" s="11" t="str">
         <x:v>SRC-HCDN-KPI-005</x:v>
@@ -9726,7 +9726,7 @@
         <x:v>DATA-HCDN-00294</x:v>
       </x:c>
       <x:c r="I294" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J294" s="11" t="str">
         <x:v>SRC-HCDN-KPI-006</x:v>
@@ -9807,7 +9807,7 @@
         <x:v>Member Services</x:v>
       </x:c>
       <x:c r="D297" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E297" s="11" t="str">
         <x:v>range</x:v>
@@ -9839,7 +9839,7 @@
         <x:v>Quality and Stars</x:v>
       </x:c>
       <x:c r="D298" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E298" s="11" t="str">
         <x:v>indexed</x:v>
@@ -9950,7 +9950,7 @@
         <x:v>DATA-HCDN-00301</x:v>
       </x:c>
       <x:c r="I301" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J301" s="11" t="str">
         <x:v>SRC-HCDN-KPI-013</x:v>
@@ -9982,7 +9982,7 @@
         <x:v>DATA-HCDN-00302</x:v>
       </x:c>
       <x:c r="I302" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J302" s="11" t="str">
         <x:v>SRC-HCDN-KPI-014</x:v>
@@ -10014,7 +10014,7 @@
         <x:v>DATA-HCDN-00303</x:v>
       </x:c>
       <x:c r="I303" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J303" s="11" t="str">
         <x:v>SRC-HCDN-KPI-015</x:v>
@@ -10046,7 +10046,7 @@
         <x:v>DATA-HCDN-00304</x:v>
       </x:c>
       <x:c r="I304" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J304" s="11" t="str">
         <x:v>SRC-HCDN-KPI-016</x:v>
@@ -10063,7 +10063,7 @@
         <x:v>Contact Center</x:v>
       </x:c>
       <x:c r="D305" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E305" s="11" t="str">
         <x:v>withheld</x:v>
@@ -10078,7 +10078,7 @@
         <x:v>DATA-HCDN-00305</x:v>
       </x:c>
       <x:c r="I305" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J305" s="11" t="str">
         <x:v>SRC-HCDN-KPI-017</x:v>
@@ -10095,7 +10095,7 @@
         <x:v>Ambulatory Care</x:v>
       </x:c>
       <x:c r="D306" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E306" s="11" t="str">
         <x:v>exact</x:v>
@@ -10110,7 +10110,7 @@
         <x:v>DATA-HCDN-00306</x:v>
       </x:c>
       <x:c r="I306" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J306" s="11" t="str">
         <x:v>SRC-HCDN-KPI-018</x:v>
@@ -10142,7 +10142,7 @@
         <x:v>DATA-HCDN-00307</x:v>
       </x:c>
       <x:c r="I307" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J307" s="11" t="str">
         <x:v>SRC-HCDN-KPI-019</x:v>
@@ -10174,7 +10174,7 @@
         <x:v>DATA-HCDN-00308</x:v>
       </x:c>
       <x:c r="I308" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J308" s="11" t="str">
         <x:v>SRC-HCDN-KPI-020</x:v>
@@ -10206,7 +10206,7 @@
         <x:v>DATA-HCDN-00309</x:v>
       </x:c>
       <x:c r="I309" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J309" s="11" t="str">
         <x:v>SRC-HCDN-KPI-021</x:v>
@@ -10238,7 +10238,7 @@
         <x:v>DATA-HCDN-00310</x:v>
       </x:c>
       <x:c r="I310" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J310" s="11" t="str">
         <x:v>SRC-HCDN-KPI-022</x:v>
@@ -10270,7 +10270,7 @@
         <x:v>DATA-HCDN-00311</x:v>
       </x:c>
       <x:c r="I311" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J311" s="11" t="str">
         <x:v>SRC-HCDN-KPI-023</x:v>
@@ -10302,7 +10302,7 @@
         <x:v>DATA-HCDN-00312</x:v>
       </x:c>
       <x:c r="I312" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J312" s="11" t="str">
         <x:v>SRC-HCDN-KPI-024</x:v>
@@ -10319,7 +10319,7 @@
         <x:v>Oncology</x:v>
       </x:c>
       <x:c r="D313" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E313" s="11" t="str">
         <x:v>indexed</x:v>
@@ -10334,7 +10334,7 @@
         <x:v>DATA-HCDN-00313</x:v>
       </x:c>
       <x:c r="I313" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J313" s="11" t="str">
         <x:v>SRC-HCDN-KPI-025</x:v>
@@ -10351,7 +10351,7 @@
         <x:v>Cardiology</x:v>
       </x:c>
       <x:c r="D314" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E314" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -10366,7 +10366,7 @@
         <x:v>DATA-HCDN-00314</x:v>
       </x:c>
       <x:c r="I314" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J314" s="11" t="str">
         <x:v>SRC-HCDN-KPI-026</x:v>
@@ -10398,7 +10398,7 @@
         <x:v>DATA-HCDN-00315</x:v>
       </x:c>
       <x:c r="I315" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J315" s="11" t="str">
         <x:v>SRC-HCDN-KPI-027</x:v>
@@ -10430,7 +10430,7 @@
         <x:v>DATA-HCDN-00316</x:v>
       </x:c>
       <x:c r="I316" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J316" s="11" t="str">
         <x:v>SRC-HCDN-KPI-028</x:v>
@@ -10462,7 +10462,7 @@
         <x:v>DATA-HCDN-00317</x:v>
       </x:c>
       <x:c r="I317" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J317" s="11" t="str">
         <x:v>SRC-HCDN-KPI-029</x:v>
@@ -10494,7 +10494,7 @@
         <x:v>DATA-HCDN-00318</x:v>
       </x:c>
       <x:c r="I318" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J318" s="11" t="str">
         <x:v>SRC-HCDN-KPI-030</x:v>
@@ -10526,7 +10526,7 @@
         <x:v>DATA-HCDN-00319</x:v>
       </x:c>
       <x:c r="I319" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J319" s="11" t="str">
         <x:v>SRC-HCDN-KPI-031</x:v>
@@ -10558,7 +10558,7 @@
         <x:v>DATA-HCDN-00320</x:v>
       </x:c>
       <x:c r="I320" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J320" s="11" t="str">
         <x:v>SRC-HCDN-KPI-032</x:v>
@@ -10575,7 +10575,7 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D321" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E321" s="11" t="str">
         <x:v>exact</x:v>
@@ -10590,7 +10590,7 @@
         <x:v>DATA-HCDN-00321</x:v>
       </x:c>
       <x:c r="I321" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J321" s="11" t="str">
         <x:v>SRC-HCDN-KPI-033</x:v>
@@ -10601,13 +10601,13 @@
         <x:v>KPI-HCDN-0321</x:v>
       </x:c>
       <x:c r="B322" s="11" t="str">
-        <x:v>Medication adherence measure 0321</x:v>
+        <x:v>HEDIS medication adherence measure 0321</x:v>
       </x:c>
       <x:c r="C322" s="11" t="str">
         <x:v>Procurement</x:v>
       </x:c>
       <x:c r="D322" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E322" s="11" t="str">
         <x:v>range</x:v>
@@ -10622,7 +10622,7 @@
         <x:v>DATA-HCDN-00322</x:v>
       </x:c>
       <x:c r="I322" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J322" s="11" t="str">
         <x:v>SRC-HCDN-KPI-034</x:v>
@@ -10633,7 +10633,7 @@
         <x:v>KPI-HCDN-0322</x:v>
       </x:c>
       <x:c r="B323" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0322</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0322</x:v>
       </x:c>
       <x:c r="C323" s="11" t="str">
         <x:v>HR</x:v>
@@ -10654,7 +10654,7 @@
         <x:v>DATA-HCDN-00323</x:v>
       </x:c>
       <x:c r="I323" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J323" s="11" t="str">
         <x:v>SRC-HCDN-KPI-035</x:v>
@@ -10665,7 +10665,7 @@
         <x:v>KPI-HCDN-0323</x:v>
       </x:c>
       <x:c r="B324" s="11" t="str">
-        <x:v>Breast cancer screening measure 0323</x:v>
+        <x:v>HEDIS breast cancer screening measure 0323</x:v>
       </x:c>
       <x:c r="C324" s="11" t="str">
         <x:v>Supply Chain</x:v>
@@ -10686,7 +10686,7 @@
         <x:v>DATA-HCDN-00324</x:v>
       </x:c>
       <x:c r="I324" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J324" s="11" t="str">
         <x:v>SRC-HCDN-KPI-036</x:v>
@@ -10718,7 +10718,7 @@
         <x:v>DATA-HCDN-00325</x:v>
       </x:c>
       <x:c r="I325" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J325" s="11" t="str">
         <x:v>SRC-HCDN-KPI-037</x:v>
@@ -10750,7 +10750,7 @@
         <x:v>DATA-HCDN-00326</x:v>
       </x:c>
       <x:c r="I326" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J326" s="11" t="str">
         <x:v>SRC-HCDN-KPI-038</x:v>
@@ -10782,7 +10782,7 @@
         <x:v>DATA-HCDN-00327</x:v>
       </x:c>
       <x:c r="I327" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J327" s="11" t="str">
         <x:v>SRC-HCDN-KPI-039</x:v>
@@ -10814,7 +10814,7 @@
         <x:v>DATA-HCDN-00328</x:v>
       </x:c>
       <x:c r="I328" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J328" s="11" t="str">
         <x:v>SRC-HCDN-KPI-040</x:v>
@@ -10831,7 +10831,7 @@
         <x:v>Clinical Operations</x:v>
       </x:c>
       <x:c r="D329" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E329" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -10846,7 +10846,7 @@
         <x:v>DATA-HCDN-00329</x:v>
       </x:c>
       <x:c r="I329" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J329" s="11" t="str">
         <x:v>SRC-HCDN-KPI-041</x:v>
@@ -10863,7 +10863,7 @@
         <x:v>Revenue Cycle</x:v>
       </x:c>
       <x:c r="D330" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E330" s="11" t="str">
         <x:v>withheld</x:v>
@@ -10878,7 +10878,7 @@
         <x:v>DATA-HCDN-00330</x:v>
       </x:c>
       <x:c r="I330" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J330" s="11" t="str">
         <x:v>SRC-HCDN-KPI-042</x:v>
@@ -10910,7 +10910,7 @@
         <x:v>DATA-HCDN-00331</x:v>
       </x:c>
       <x:c r="I331" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J331" s="11" t="str">
         <x:v>SRC-HCDN-KPI-043</x:v>
@@ -10942,7 +10942,7 @@
         <x:v>DATA-HCDN-00332</x:v>
       </x:c>
       <x:c r="I332" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J332" s="11" t="str">
         <x:v>SRC-HCDN-KPI-044</x:v>
@@ -10974,7 +10974,7 @@
         <x:v>DATA-HCDN-00333</x:v>
       </x:c>
       <x:c r="I333" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J333" s="11" t="str">
         <x:v>SRC-HCDN-KPI-045</x:v>
@@ -11006,7 +11006,7 @@
         <x:v>DATA-HCDN-00334</x:v>
       </x:c>
       <x:c r="I334" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J334" s="11" t="str">
         <x:v>SRC-HCDN-KPI-046</x:v>
@@ -11038,7 +11038,7 @@
         <x:v>DATA-HCDN-00335</x:v>
       </x:c>
       <x:c r="I335" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J335" s="11" t="str">
         <x:v>SRC-HCDN-KPI-047</x:v>
@@ -11070,7 +11070,7 @@
         <x:v>DATA-HCDN-00336</x:v>
       </x:c>
       <x:c r="I336" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J336" s="11" t="str">
         <x:v>SRC-HCDN-KPI-048</x:v>
@@ -11087,7 +11087,7 @@
         <x:v>Utilization Management</x:v>
       </x:c>
       <x:c r="D337" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E337" s="11" t="str">
         <x:v>range</x:v>
@@ -11119,7 +11119,7 @@
         <x:v>Member Services</x:v>
       </x:c>
       <x:c r="D338" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E338" s="11" t="str">
         <x:v>indexed</x:v>
@@ -11294,7 +11294,7 @@
         <x:v>DATA-HCDN-00343</x:v>
       </x:c>
       <x:c r="I343" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J343" s="11" t="str">
         <x:v>SRC-HCDN-KPI-055</x:v>
@@ -11326,7 +11326,7 @@
         <x:v>DATA-HCDN-00344</x:v>
       </x:c>
       <x:c r="I344" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J344" s="11" t="str">
         <x:v>SRC-HCDN-KPI-056</x:v>
@@ -11343,7 +11343,7 @@
         <x:v>Digital Front Door</x:v>
       </x:c>
       <x:c r="D345" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E345" s="11" t="str">
         <x:v>withheld</x:v>
@@ -11358,7 +11358,7 @@
         <x:v>DATA-HCDN-00345</x:v>
       </x:c>
       <x:c r="I345" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J345" s="11" t="str">
         <x:v>SRC-HCDN-KPI-057</x:v>
@@ -11375,7 +11375,7 @@
         <x:v>Contact Center</x:v>
       </x:c>
       <x:c r="D346" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E346" s="11" t="str">
         <x:v>exact</x:v>
@@ -11390,7 +11390,7 @@
         <x:v>DATA-HCDN-00346</x:v>
       </x:c>
       <x:c r="I346" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J346" s="11" t="str">
         <x:v>SRC-HCDN-KPI-058</x:v>
@@ -11422,7 +11422,7 @@
         <x:v>DATA-HCDN-00347</x:v>
       </x:c>
       <x:c r="I347" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J347" s="11" t="str">
         <x:v>SRC-HCDN-KPI-059</x:v>
@@ -11454,7 +11454,7 @@
         <x:v>DATA-HCDN-00348</x:v>
       </x:c>
       <x:c r="I348" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J348" s="11" t="str">
         <x:v>SRC-HCDN-KPI-060</x:v>
@@ -11486,7 +11486,7 @@
         <x:v>DATA-HCDN-00349</x:v>
       </x:c>
       <x:c r="I349" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J349" s="11" t="str">
         <x:v>SRC-HCDN-KPI-061</x:v>
@@ -11518,7 +11518,7 @@
         <x:v>DATA-HCDN-00350</x:v>
       </x:c>
       <x:c r="I350" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J350" s="11" t="str">
         <x:v>SRC-HCDN-KPI-062</x:v>
@@ -11550,7 +11550,7 @@
         <x:v>DATA-HCDN-00351</x:v>
       </x:c>
       <x:c r="I351" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J351" s="11" t="str">
         <x:v>SRC-HCDN-KPI-063</x:v>
@@ -11582,7 +11582,7 @@
         <x:v>DATA-HCDN-00352</x:v>
       </x:c>
       <x:c r="I352" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J352" s="11" t="str">
         <x:v>SRC-HCDN-KPI-064</x:v>
@@ -11599,7 +11599,7 @@
         <x:v>Pharmacy</x:v>
       </x:c>
       <x:c r="D353" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E353" s="11" t="str">
         <x:v>indexed</x:v>
@@ -11614,7 +11614,7 @@
         <x:v>DATA-HCDN-00353</x:v>
       </x:c>
       <x:c r="I353" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J353" s="11" t="str">
         <x:v>SRC-HCDN-KPI-065</x:v>
@@ -11625,13 +11625,13 @@
         <x:v>KPI-HCDN-0353</x:v>
       </x:c>
       <x:c r="B354" s="11" t="str">
-        <x:v>Medication adherence measure 0353</x:v>
+        <x:v>HEDIS medication adherence measure 0353</x:v>
       </x:c>
       <x:c r="C354" s="11" t="str">
         <x:v>Oncology</x:v>
       </x:c>
       <x:c r="D354" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E354" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -11646,7 +11646,7 @@
         <x:v>DATA-HCDN-00354</x:v>
       </x:c>
       <x:c r="I354" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J354" s="11" t="str">
         <x:v>SRC-HCDN-KPI-066</x:v>
@@ -11657,7 +11657,7 @@
         <x:v>KPI-HCDN-0354</x:v>
       </x:c>
       <x:c r="B355" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0354</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0354</x:v>
       </x:c>
       <x:c r="C355" s="11" t="str">
         <x:v>Cardiology</x:v>
@@ -11678,7 +11678,7 @@
         <x:v>DATA-HCDN-00355</x:v>
       </x:c>
       <x:c r="I355" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J355" s="11" t="str">
         <x:v>SRC-HCDN-KPI-067</x:v>
@@ -11689,7 +11689,7 @@
         <x:v>KPI-HCDN-0355</x:v>
       </x:c>
       <x:c r="B356" s="11" t="str">
-        <x:v>Breast cancer screening measure 0355</x:v>
+        <x:v>HEDIS breast cancer screening measure 0355</x:v>
       </x:c>
       <x:c r="C356" s="11" t="str">
         <x:v>Data and Analytics</x:v>
@@ -11710,7 +11710,7 @@
         <x:v>DATA-HCDN-00356</x:v>
       </x:c>
       <x:c r="I356" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J356" s="11" t="str">
         <x:v>SRC-HCDN-KPI-068</x:v>
@@ -11742,7 +11742,7 @@
         <x:v>DATA-HCDN-00357</x:v>
       </x:c>
       <x:c r="I357" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J357" s="11" t="str">
         <x:v>SRC-HCDN-KPI-069</x:v>
@@ -11774,7 +11774,7 @@
         <x:v>DATA-HCDN-00358</x:v>
       </x:c>
       <x:c r="I358" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J358" s="11" t="str">
         <x:v>SRC-HCDN-KPI-070</x:v>
@@ -11806,7 +11806,7 @@
         <x:v>DATA-HCDN-00359</x:v>
       </x:c>
       <x:c r="I359" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J359" s="11" t="str">
         <x:v>SRC-HCDN-KPI-071</x:v>
@@ -11838,7 +11838,7 @@
         <x:v>DATA-HCDN-00360</x:v>
       </x:c>
       <x:c r="I360" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J360" s="11" t="str">
         <x:v>SRC-HCDN-KPI-072</x:v>
@@ -11855,7 +11855,7 @@
         <x:v>Technology</x:v>
       </x:c>
       <x:c r="D361" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E361" s="11" t="str">
         <x:v>exact</x:v>
@@ -11870,7 +11870,7 @@
         <x:v>DATA-HCDN-00361</x:v>
       </x:c>
       <x:c r="I361" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J361" s="11" t="str">
         <x:v>SRC-HCDN-KPI-073</x:v>
@@ -11887,7 +11887,7 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D362" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E362" s="11" t="str">
         <x:v>range</x:v>
@@ -11902,7 +11902,7 @@
         <x:v>DATA-HCDN-00362</x:v>
       </x:c>
       <x:c r="I362" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J362" s="11" t="str">
         <x:v>SRC-HCDN-KPI-074</x:v>
@@ -11934,7 +11934,7 @@
         <x:v>DATA-HCDN-00363</x:v>
       </x:c>
       <x:c r="I363" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J363" s="11" t="str">
         <x:v>SRC-HCDN-KPI-075</x:v>
@@ -11966,7 +11966,7 @@
         <x:v>DATA-HCDN-00364</x:v>
       </x:c>
       <x:c r="I364" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J364" s="11" t="str">
         <x:v>SRC-HCDN-KPI-076</x:v>
@@ -11998,7 +11998,7 @@
         <x:v>DATA-HCDN-00365</x:v>
       </x:c>
       <x:c r="I365" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J365" s="11" t="str">
         <x:v>SRC-HCDN-KPI-077</x:v>
@@ -12030,7 +12030,7 @@
         <x:v>DATA-HCDN-00366</x:v>
       </x:c>
       <x:c r="I366" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J366" s="11" t="str">
         <x:v>SRC-HCDN-KPI-078</x:v>
@@ -12062,7 +12062,7 @@
         <x:v>DATA-HCDN-00367</x:v>
       </x:c>
       <x:c r="I367" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J367" s="11" t="str">
         <x:v>SRC-HCDN-KPI-079</x:v>
@@ -12094,7 +12094,7 @@
         <x:v>DATA-HCDN-00368</x:v>
       </x:c>
       <x:c r="I368" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J368" s="11" t="str">
         <x:v>SRC-HCDN-KPI-080</x:v>
@@ -12111,7 +12111,7 @@
         <x:v>Value-Based Care</x:v>
       </x:c>
       <x:c r="D369" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E369" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -12126,7 +12126,7 @@
         <x:v>DATA-HCDN-00369</x:v>
       </x:c>
       <x:c r="I369" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J369" s="11" t="str">
         <x:v>SRC-HCDN-KPI-081</x:v>
@@ -12143,7 +12143,7 @@
         <x:v>Clinical Operations</x:v>
       </x:c>
       <x:c r="D370" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E370" s="11" t="str">
         <x:v>withheld</x:v>
@@ -12158,7 +12158,7 @@
         <x:v>DATA-HCDN-00370</x:v>
       </x:c>
       <x:c r="I370" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J370" s="11" t="str">
         <x:v>SRC-HCDN-KPI-082</x:v>
@@ -12190,7 +12190,7 @@
         <x:v>DATA-HCDN-00371</x:v>
       </x:c>
       <x:c r="I371" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J371" s="11" t="str">
         <x:v>SRC-HCDN-KPI-083</x:v>
@@ -12222,7 +12222,7 @@
         <x:v>DATA-HCDN-00372</x:v>
       </x:c>
       <x:c r="I372" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J372" s="11" t="str">
         <x:v>SRC-HCDN-KPI-084</x:v>
@@ -12254,7 +12254,7 @@
         <x:v>DATA-HCDN-00373</x:v>
       </x:c>
       <x:c r="I373" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J373" s="11" t="str">
         <x:v>SRC-HCDN-KPI-085</x:v>
@@ -12286,7 +12286,7 @@
         <x:v>DATA-HCDN-00374</x:v>
       </x:c>
       <x:c r="I374" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J374" s="11" t="str">
         <x:v>SRC-HCDN-KPI-086</x:v>
@@ -12318,7 +12318,7 @@
         <x:v>DATA-HCDN-00375</x:v>
       </x:c>
       <x:c r="I375" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J375" s="11" t="str">
         <x:v>SRC-HCDN-KPI-087</x:v>
@@ -12350,7 +12350,7 @@
         <x:v>DATA-HCDN-00376</x:v>
       </x:c>
       <x:c r="I376" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J376" s="11" t="str">
         <x:v>SRC-HCDN-KPI-088</x:v>
@@ -12367,7 +12367,7 @@
         <x:v>Claims Operations</x:v>
       </x:c>
       <x:c r="D377" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E377" s="11" t="str">
         <x:v>range</x:v>
@@ -12382,7 +12382,7 @@
         <x:v>DATA-HCDN-00377</x:v>
       </x:c>
       <x:c r="I377" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J377" s="11" t="str">
         <x:v>SRC-HCDN-KPI-089</x:v>
@@ -12399,7 +12399,7 @@
         <x:v>Utilization Management</x:v>
       </x:c>
       <x:c r="D378" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E378" s="11" t="str">
         <x:v>indexed</x:v>
@@ -12414,7 +12414,7 @@
         <x:v>DATA-HCDN-00378</x:v>
       </x:c>
       <x:c r="I378" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J378" s="11" t="str">
         <x:v>SRC-HCDN-KPI-090</x:v>
@@ -12623,7 +12623,7 @@
         <x:v>Payer Contracting</x:v>
       </x:c>
       <x:c r="D385" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E385" s="11" t="str">
         <x:v>withheld</x:v>
@@ -12638,7 +12638,7 @@
         <x:v>DATA-HCDN-00385</x:v>
       </x:c>
       <x:c r="I385" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J385" s="11" t="str">
         <x:v>SRC-HCDN-KPI-001</x:v>
@@ -12649,13 +12649,13 @@
         <x:v>KPI-HCDN-0385</x:v>
       </x:c>
       <x:c r="B386" s="11" t="str">
-        <x:v>Medication adherence measure 0385</x:v>
+        <x:v>HEDIS medication adherence measure 0385</x:v>
       </x:c>
       <x:c r="C386" s="11" t="str">
         <x:v>Digital Front Door</x:v>
       </x:c>
       <x:c r="D386" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E386" s="11" t="str">
         <x:v>exact</x:v>
@@ -12670,7 +12670,7 @@
         <x:v>DATA-HCDN-00386</x:v>
       </x:c>
       <x:c r="I386" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J386" s="11" t="str">
         <x:v>SRC-HCDN-KPI-002</x:v>
@@ -12681,7 +12681,7 @@
         <x:v>KPI-HCDN-0386</x:v>
       </x:c>
       <x:c r="B387" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0386</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0386</x:v>
       </x:c>
       <x:c r="C387" s="11" t="str">
         <x:v>Contact Center</x:v>
@@ -12702,7 +12702,7 @@
         <x:v>DATA-HCDN-00387</x:v>
       </x:c>
       <x:c r="I387" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J387" s="11" t="str">
         <x:v>SRC-HCDN-KPI-003</x:v>
@@ -12713,7 +12713,7 @@
         <x:v>KPI-HCDN-0387</x:v>
       </x:c>
       <x:c r="B388" s="11" t="str">
-        <x:v>Breast cancer screening measure 0387</x:v>
+        <x:v>HEDIS breast cancer screening measure 0387</x:v>
       </x:c>
       <x:c r="C388" s="11" t="str">
         <x:v>Ambulatory Care</x:v>
@@ -12734,7 +12734,7 @@
         <x:v>DATA-HCDN-00388</x:v>
       </x:c>
       <x:c r="I388" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J388" s="11" t="str">
         <x:v>SRC-HCDN-KPI-004</x:v>
@@ -12766,7 +12766,7 @@
         <x:v>DATA-HCDN-00389</x:v>
       </x:c>
       <x:c r="I389" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J389" s="11" t="str">
         <x:v>SRC-HCDN-KPI-005</x:v>
@@ -12798,7 +12798,7 @@
         <x:v>DATA-HCDN-00390</x:v>
       </x:c>
       <x:c r="I390" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J390" s="11" t="str">
         <x:v>SRC-HCDN-KPI-006</x:v>
@@ -12830,7 +12830,7 @@
         <x:v>DATA-HCDN-00391</x:v>
       </x:c>
       <x:c r="I391" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J391" s="11" t="str">
         <x:v>SRC-HCDN-KPI-007</x:v>
@@ -12862,7 +12862,7 @@
         <x:v>DATA-HCDN-00392</x:v>
       </x:c>
       <x:c r="I392" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J392" s="11" t="str">
         <x:v>SRC-HCDN-KPI-008</x:v>
@@ -12879,7 +12879,7 @@
         <x:v>Lab</x:v>
       </x:c>
       <x:c r="D393" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E393" s="11" t="str">
         <x:v>indexed</x:v>
@@ -12894,7 +12894,7 @@
         <x:v>DATA-HCDN-00393</x:v>
       </x:c>
       <x:c r="I393" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J393" s="11" t="str">
         <x:v>SRC-HCDN-KPI-009</x:v>
@@ -12911,7 +12911,7 @@
         <x:v>Pharmacy</x:v>
       </x:c>
       <x:c r="D394" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E394" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -12926,7 +12926,7 @@
         <x:v>DATA-HCDN-00394</x:v>
       </x:c>
       <x:c r="I394" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J394" s="11" t="str">
         <x:v>SRC-HCDN-KPI-010</x:v>
@@ -12958,7 +12958,7 @@
         <x:v>DATA-HCDN-00395</x:v>
       </x:c>
       <x:c r="I395" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J395" s="11" t="str">
         <x:v>SRC-HCDN-KPI-011</x:v>
@@ -12990,7 +12990,7 @@
         <x:v>DATA-HCDN-00396</x:v>
       </x:c>
       <x:c r="I396" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J396" s="11" t="str">
         <x:v>SRC-HCDN-KPI-012</x:v>
@@ -13022,7 +13022,7 @@
         <x:v>DATA-HCDN-00397</x:v>
       </x:c>
       <x:c r="I397" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J397" s="11" t="str">
         <x:v>SRC-HCDN-KPI-013</x:v>
@@ -13054,7 +13054,7 @@
         <x:v>DATA-HCDN-00398</x:v>
       </x:c>
       <x:c r="I398" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J398" s="11" t="str">
         <x:v>SRC-HCDN-KPI-014</x:v>
@@ -13086,7 +13086,7 @@
         <x:v>DATA-HCDN-00399</x:v>
       </x:c>
       <x:c r="I399" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J399" s="11" t="str">
         <x:v>SRC-HCDN-KPI-015</x:v>
@@ -13118,7 +13118,7 @@
         <x:v>DATA-HCDN-00400</x:v>
       </x:c>
       <x:c r="I400" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J400" s="11" t="str">
         <x:v>SRC-HCDN-KPI-016</x:v>
@@ -13135,7 +13135,7 @@
         <x:v>AI Transformation</x:v>
       </x:c>
       <x:c r="D401" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E401" s="11" t="str">
         <x:v>exact</x:v>
@@ -13150,7 +13150,7 @@
         <x:v>DATA-HCDN-00401</x:v>
       </x:c>
       <x:c r="I401" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J401" s="11" t="str">
         <x:v>SRC-HCDN-KPI-017</x:v>
@@ -13167,7 +13167,7 @@
         <x:v>Technology</x:v>
       </x:c>
       <x:c r="D402" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E402" s="11" t="str">
         <x:v>range</x:v>
@@ -13182,7 +13182,7 @@
         <x:v>DATA-HCDN-00402</x:v>
       </x:c>
       <x:c r="I402" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J402" s="11" t="str">
         <x:v>SRC-HCDN-KPI-018</x:v>
@@ -13214,7 +13214,7 @@
         <x:v>DATA-HCDN-00403</x:v>
       </x:c>
       <x:c r="I403" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J403" s="11" t="str">
         <x:v>SRC-HCDN-KPI-019</x:v>
@@ -13246,7 +13246,7 @@
         <x:v>DATA-HCDN-00404</x:v>
       </x:c>
       <x:c r="I404" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J404" s="11" t="str">
         <x:v>SRC-HCDN-KPI-020</x:v>
@@ -13278,7 +13278,7 @@
         <x:v>DATA-HCDN-00405</x:v>
       </x:c>
       <x:c r="I405" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J405" s="11" t="str">
         <x:v>SRC-HCDN-KPI-021</x:v>
@@ -13310,7 +13310,7 @@
         <x:v>DATA-HCDN-00406</x:v>
       </x:c>
       <x:c r="I406" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J406" s="11" t="str">
         <x:v>SRC-HCDN-KPI-022</x:v>
@@ -13342,7 +13342,7 @@
         <x:v>DATA-HCDN-00407</x:v>
       </x:c>
       <x:c r="I407" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J407" s="11" t="str">
         <x:v>SRC-HCDN-KPI-023</x:v>
@@ -13374,7 +13374,7 @@
         <x:v>DATA-HCDN-00408</x:v>
       </x:c>
       <x:c r="I408" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J408" s="11" t="str">
         <x:v>SRC-HCDN-KPI-024</x:v>
@@ -13391,7 +13391,7 @@
         <x:v>Provider Network</x:v>
       </x:c>
       <x:c r="D409" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E409" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -13406,7 +13406,7 @@
         <x:v>DATA-HCDN-00409</x:v>
       </x:c>
       <x:c r="I409" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J409" s="11" t="str">
         <x:v>SRC-HCDN-KPI-025</x:v>
@@ -13423,7 +13423,7 @@
         <x:v>Value-Based Care</x:v>
       </x:c>
       <x:c r="D410" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E410" s="11" t="str">
         <x:v>withheld</x:v>
@@ -13438,7 +13438,7 @@
         <x:v>DATA-HCDN-00410</x:v>
       </x:c>
       <x:c r="I410" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J410" s="11" t="str">
         <x:v>SRC-HCDN-KPI-026</x:v>
@@ -13470,7 +13470,7 @@
         <x:v>DATA-HCDN-00411</x:v>
       </x:c>
       <x:c r="I411" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J411" s="11" t="str">
         <x:v>SRC-HCDN-KPI-027</x:v>
@@ -13502,7 +13502,7 @@
         <x:v>DATA-HCDN-00412</x:v>
       </x:c>
       <x:c r="I412" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J412" s="11" t="str">
         <x:v>SRC-HCDN-KPI-028</x:v>
@@ -13534,7 +13534,7 @@
         <x:v>DATA-HCDN-00413</x:v>
       </x:c>
       <x:c r="I413" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J413" s="11" t="str">
         <x:v>SRC-HCDN-KPI-029</x:v>
@@ -13566,7 +13566,7 @@
         <x:v>DATA-HCDN-00414</x:v>
       </x:c>
       <x:c r="I414" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J414" s="11" t="str">
         <x:v>SRC-HCDN-KPI-030</x:v>
@@ -13598,7 +13598,7 @@
         <x:v>DATA-HCDN-00415</x:v>
       </x:c>
       <x:c r="I415" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J415" s="11" t="str">
         <x:v>SRC-HCDN-KPI-031</x:v>
@@ -13630,7 +13630,7 @@
         <x:v>DATA-HCDN-00416</x:v>
       </x:c>
       <x:c r="I416" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J416" s="11" t="str">
         <x:v>SRC-HCDN-KPI-032</x:v>
@@ -13647,7 +13647,7 @@
         <x:v>Medicare Advantage</x:v>
       </x:c>
       <x:c r="D417" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E417" s="11" t="str">
         <x:v>range</x:v>
@@ -13662,7 +13662,7 @@
         <x:v>DATA-HCDN-00417</x:v>
       </x:c>
       <x:c r="I417" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J417" s="11" t="str">
         <x:v>SRC-HCDN-KPI-033</x:v>
@@ -13673,13 +13673,13 @@
         <x:v>KPI-HCDN-0417</x:v>
       </x:c>
       <x:c r="B418" s="11" t="str">
-        <x:v>Medication adherence measure 0417</x:v>
+        <x:v>HEDIS medication adherence measure 0417</x:v>
       </x:c>
       <x:c r="C418" s="11" t="str">
         <x:v>Claims Operations</x:v>
       </x:c>
       <x:c r="D418" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E418" s="11" t="str">
         <x:v>indexed</x:v>
@@ -13694,7 +13694,7 @@
         <x:v>DATA-HCDN-00418</x:v>
       </x:c>
       <x:c r="I418" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J418" s="11" t="str">
         <x:v>SRC-HCDN-KPI-034</x:v>
@@ -13705,7 +13705,7 @@
         <x:v>KPI-HCDN-0418</x:v>
       </x:c>
       <x:c r="B419" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0418</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0418</x:v>
       </x:c>
       <x:c r="C419" s="11" t="str">
         <x:v>Utilization Management</x:v>
@@ -13726,7 +13726,7 @@
         <x:v>DATA-HCDN-00419</x:v>
       </x:c>
       <x:c r="I419" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J419" s="11" t="str">
         <x:v>SRC-HCDN-KPI-035</x:v>
@@ -13737,7 +13737,7 @@
         <x:v>KPI-HCDN-0419</x:v>
       </x:c>
       <x:c r="B420" s="11" t="str">
-        <x:v>Breast cancer screening measure 0419</x:v>
+        <x:v>HEDIS breast cancer screening measure 0419</x:v>
       </x:c>
       <x:c r="C420" s="11" t="str">
         <x:v>Member Services</x:v>
@@ -13758,7 +13758,7 @@
         <x:v>DATA-HCDN-00420</x:v>
       </x:c>
       <x:c r="I420" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J420" s="11" t="str">
         <x:v>SRC-HCDN-KPI-036</x:v>
@@ -13903,7 +13903,7 @@
         <x:v>Coding</x:v>
       </x:c>
       <x:c r="D425" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E425" s="11" t="str">
         <x:v>withheld</x:v>
@@ -13935,7 +13935,7 @@
         <x:v>Payer Contracting</x:v>
       </x:c>
       <x:c r="D426" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E426" s="11" t="str">
         <x:v>exact</x:v>
@@ -13982,7 +13982,7 @@
         <x:v>DATA-HCDN-00427</x:v>
       </x:c>
       <x:c r="I427" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J427" s="11" t="str">
         <x:v>SRC-HCDN-KPI-043</x:v>
@@ -14014,7 +14014,7 @@
         <x:v>DATA-HCDN-00428</x:v>
       </x:c>
       <x:c r="I428" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J428" s="11" t="str">
         <x:v>SRC-HCDN-KPI-044</x:v>
@@ -14046,7 +14046,7 @@
         <x:v>DATA-HCDN-00429</x:v>
       </x:c>
       <x:c r="I429" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J429" s="11" t="str">
         <x:v>SRC-HCDN-KPI-045</x:v>
@@ -14078,7 +14078,7 @@
         <x:v>DATA-HCDN-00430</x:v>
       </x:c>
       <x:c r="I430" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J430" s="11" t="str">
         <x:v>SRC-HCDN-KPI-046</x:v>
@@ -14110,7 +14110,7 @@
         <x:v>DATA-HCDN-00431</x:v>
       </x:c>
       <x:c r="I431" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J431" s="11" t="str">
         <x:v>SRC-HCDN-KPI-047</x:v>
@@ -14142,7 +14142,7 @@
         <x:v>DATA-HCDN-00432</x:v>
       </x:c>
       <x:c r="I432" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J432" s="11" t="str">
         <x:v>SRC-HCDN-KPI-048</x:v>
@@ -14159,7 +14159,7 @@
         <x:v>Imaging</x:v>
       </x:c>
       <x:c r="D433" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E433" s="11" t="str">
         <x:v>indexed</x:v>
@@ -14174,7 +14174,7 @@
         <x:v>DATA-HCDN-00433</x:v>
       </x:c>
       <x:c r="I433" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J433" s="11" t="str">
         <x:v>SRC-HCDN-KPI-049</x:v>
@@ -14191,7 +14191,7 @@
         <x:v>Lab</x:v>
       </x:c>
       <x:c r="D434" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E434" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -14206,7 +14206,7 @@
         <x:v>DATA-HCDN-00434</x:v>
       </x:c>
       <x:c r="I434" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J434" s="11" t="str">
         <x:v>SRC-HCDN-KPI-050</x:v>
@@ -14238,7 +14238,7 @@
         <x:v>DATA-HCDN-00435</x:v>
       </x:c>
       <x:c r="I435" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J435" s="11" t="str">
         <x:v>SRC-HCDN-KPI-051</x:v>
@@ -14270,7 +14270,7 @@
         <x:v>DATA-HCDN-00436</x:v>
       </x:c>
       <x:c r="I436" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J436" s="11" t="str">
         <x:v>SRC-HCDN-KPI-052</x:v>
@@ -14302,7 +14302,7 @@
         <x:v>DATA-HCDN-00437</x:v>
       </x:c>
       <x:c r="I437" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J437" s="11" t="str">
         <x:v>SRC-HCDN-KPI-053</x:v>
@@ -14334,7 +14334,7 @@
         <x:v>DATA-HCDN-00438</x:v>
       </x:c>
       <x:c r="I438" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J438" s="11" t="str">
         <x:v>SRC-HCDN-KPI-054</x:v>
@@ -14366,7 +14366,7 @@
         <x:v>DATA-HCDN-00439</x:v>
       </x:c>
       <x:c r="I439" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J439" s="11" t="str">
         <x:v>SRC-HCDN-KPI-055</x:v>
@@ -14398,7 +14398,7 @@
         <x:v>DATA-HCDN-00440</x:v>
       </x:c>
       <x:c r="I440" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J440" s="11" t="str">
         <x:v>SRC-HCDN-KPI-056</x:v>
@@ -14415,7 +14415,7 @@
         <x:v>Departmental Reporting</x:v>
       </x:c>
       <x:c r="D441" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E441" s="11" t="str">
         <x:v>exact</x:v>
@@ -14430,7 +14430,7 @@
         <x:v>DATA-HCDN-00441</x:v>
       </x:c>
       <x:c r="I441" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J441" s="11" t="str">
         <x:v>SRC-HCDN-KPI-057</x:v>
@@ -14447,7 +14447,7 @@
         <x:v>AI Transformation</x:v>
       </x:c>
       <x:c r="D442" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E442" s="11" t="str">
         <x:v>range</x:v>
@@ -14462,7 +14462,7 @@
         <x:v>DATA-HCDN-00442</x:v>
       </x:c>
       <x:c r="I442" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J442" s="11" t="str">
         <x:v>SRC-HCDN-KPI-058</x:v>
@@ -14494,7 +14494,7 @@
         <x:v>DATA-HCDN-00443</x:v>
       </x:c>
       <x:c r="I443" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J443" s="11" t="str">
         <x:v>SRC-HCDN-KPI-059</x:v>
@@ -14526,7 +14526,7 @@
         <x:v>DATA-HCDN-00444</x:v>
       </x:c>
       <x:c r="I444" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J444" s="11" t="str">
         <x:v>SRC-HCDN-KPI-060</x:v>
@@ -14558,7 +14558,7 @@
         <x:v>DATA-HCDN-00445</x:v>
       </x:c>
       <x:c r="I445" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J445" s="11" t="str">
         <x:v>SRC-HCDN-KPI-061</x:v>
@@ -14590,7 +14590,7 @@
         <x:v>DATA-HCDN-00446</x:v>
       </x:c>
       <x:c r="I446" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J446" s="11" t="str">
         <x:v>SRC-HCDN-KPI-062</x:v>
@@ -14622,7 +14622,7 @@
         <x:v>DATA-HCDN-00447</x:v>
       </x:c>
       <x:c r="I447" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J447" s="11" t="str">
         <x:v>SRC-HCDN-KPI-063</x:v>
@@ -14654,7 +14654,7 @@
         <x:v>DATA-HCDN-00448</x:v>
       </x:c>
       <x:c r="I448" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J448" s="11" t="str">
         <x:v>SRC-HCDN-KPI-064</x:v>
@@ -14671,7 +14671,7 @@
         <x:v>Compliance</x:v>
       </x:c>
       <x:c r="D449" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E449" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -14686,7 +14686,7 @@
         <x:v>DATA-HCDN-00449</x:v>
       </x:c>
       <x:c r="I449" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J449" s="11" t="str">
         <x:v>SRC-HCDN-KPI-065</x:v>
@@ -14697,13 +14697,13 @@
         <x:v>KPI-HCDN-0449</x:v>
       </x:c>
       <x:c r="B450" s="11" t="str">
-        <x:v>Medication adherence measure 0449</x:v>
+        <x:v>HEDIS medication adherence measure 0449</x:v>
       </x:c>
       <x:c r="C450" s="11" t="str">
         <x:v>Provider Network</x:v>
       </x:c>
       <x:c r="D450" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E450" s="11" t="str">
         <x:v>withheld</x:v>
@@ -14718,7 +14718,7 @@
         <x:v>DATA-HCDN-00450</x:v>
       </x:c>
       <x:c r="I450" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J450" s="11" t="str">
         <x:v>SRC-HCDN-KPI-066</x:v>
@@ -14729,7 +14729,7 @@
         <x:v>KPI-HCDN-0450</x:v>
       </x:c>
       <x:c r="B451" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0450</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0450</x:v>
       </x:c>
       <x:c r="C451" s="11" t="str">
         <x:v>Value-Based Care</x:v>
@@ -14750,7 +14750,7 @@
         <x:v>DATA-HCDN-00451</x:v>
       </x:c>
       <x:c r="I451" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J451" s="11" t="str">
         <x:v>SRC-HCDN-KPI-067</x:v>
@@ -14761,7 +14761,7 @@
         <x:v>KPI-HCDN-0451</x:v>
       </x:c>
       <x:c r="B452" s="11" t="str">
-        <x:v>Breast cancer screening measure 0451</x:v>
+        <x:v>HEDIS breast cancer screening measure 0451</x:v>
       </x:c>
       <x:c r="C452" s="11" t="str">
         <x:v>Clinical Operations</x:v>
@@ -14782,7 +14782,7 @@
         <x:v>DATA-HCDN-00452</x:v>
       </x:c>
       <x:c r="I452" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J452" s="11" t="str">
         <x:v>SRC-HCDN-KPI-068</x:v>
@@ -14814,7 +14814,7 @@
         <x:v>DATA-HCDN-00453</x:v>
       </x:c>
       <x:c r="I453" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J453" s="11" t="str">
         <x:v>SRC-HCDN-KPI-069</x:v>
@@ -14846,7 +14846,7 @@
         <x:v>DATA-HCDN-00454</x:v>
       </x:c>
       <x:c r="I454" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J454" s="11" t="str">
         <x:v>SRC-HCDN-KPI-070</x:v>
@@ -14878,7 +14878,7 @@
         <x:v>DATA-HCDN-00455</x:v>
       </x:c>
       <x:c r="I455" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J455" s="11" t="str">
         <x:v>SRC-HCDN-KPI-071</x:v>
@@ -14910,7 +14910,7 @@
         <x:v>DATA-HCDN-00456</x:v>
       </x:c>
       <x:c r="I456" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J456" s="11" t="str">
         <x:v>SRC-HCDN-KPI-072</x:v>
@@ -14927,7 +14927,7 @@
         <x:v>Health Plan Operations</x:v>
       </x:c>
       <x:c r="D457" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E457" s="11" t="str">
         <x:v>range</x:v>
@@ -14942,7 +14942,7 @@
         <x:v>DATA-HCDN-00457</x:v>
       </x:c>
       <x:c r="I457" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J457" s="11" t="str">
         <x:v>SRC-HCDN-KPI-073</x:v>
@@ -14959,7 +14959,7 @@
         <x:v>Medicare Advantage</x:v>
       </x:c>
       <x:c r="D458" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E458" s="11" t="str">
         <x:v>indexed</x:v>
@@ -14974,7 +14974,7 @@
         <x:v>DATA-HCDN-00458</x:v>
       </x:c>
       <x:c r="I458" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J458" s="11" t="str">
         <x:v>SRC-HCDN-KPI-074</x:v>
@@ -15006,7 +15006,7 @@
         <x:v>DATA-HCDN-00459</x:v>
       </x:c>
       <x:c r="I459" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J459" s="11" t="str">
         <x:v>SRC-HCDN-KPI-075</x:v>
@@ -15038,7 +15038,7 @@
         <x:v>DATA-HCDN-00460</x:v>
       </x:c>
       <x:c r="I460" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J460" s="11" t="str">
         <x:v>SRC-HCDN-KPI-076</x:v>
@@ -15070,7 +15070,7 @@
         <x:v>DATA-HCDN-00461</x:v>
       </x:c>
       <x:c r="I461" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J461" s="11" t="str">
         <x:v>SRC-HCDN-KPI-077</x:v>
@@ -15102,7 +15102,7 @@
         <x:v>DATA-HCDN-00462</x:v>
       </x:c>
       <x:c r="I462" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J462" s="11" t="str">
         <x:v>SRC-HCDN-KPI-078</x:v>
@@ -15183,7 +15183,7 @@
         <x:v>Finance</x:v>
       </x:c>
       <x:c r="D465" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E465" s="11" t="str">
         <x:v>withheld</x:v>
@@ -15215,7 +15215,7 @@
         <x:v>Coding</x:v>
       </x:c>
       <x:c r="D466" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E466" s="11" t="str">
         <x:v>exact</x:v>
@@ -15326,7 +15326,7 @@
         <x:v>DATA-HCDN-00469</x:v>
       </x:c>
       <x:c r="I469" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J469" s="11" t="str">
         <x:v>SRC-HCDN-KPI-085</x:v>
@@ -15358,7 +15358,7 @@
         <x:v>DATA-HCDN-00470</x:v>
       </x:c>
       <x:c r="I470" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J470" s="11" t="str">
         <x:v>SRC-HCDN-KPI-086</x:v>
@@ -15390,7 +15390,7 @@
         <x:v>DATA-HCDN-00471</x:v>
       </x:c>
       <x:c r="I471" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J471" s="11" t="str">
         <x:v>SRC-HCDN-KPI-087</x:v>
@@ -15422,7 +15422,7 @@
         <x:v>DATA-HCDN-00472</x:v>
       </x:c>
       <x:c r="I472" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J472" s="11" t="str">
         <x:v>SRC-HCDN-KPI-088</x:v>
@@ -15439,7 +15439,7 @@
         <x:v>Surgery</x:v>
       </x:c>
       <x:c r="D473" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E473" s="11" t="str">
         <x:v>indexed</x:v>
@@ -15454,7 +15454,7 @@
         <x:v>DATA-HCDN-00473</x:v>
       </x:c>
       <x:c r="I473" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J473" s="11" t="str">
         <x:v>SRC-HCDN-KPI-089</x:v>
@@ -15471,7 +15471,7 @@
         <x:v>Imaging</x:v>
       </x:c>
       <x:c r="D474" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E474" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -15486,7 +15486,7 @@
         <x:v>DATA-HCDN-00474</x:v>
       </x:c>
       <x:c r="I474" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J474" s="11" t="str">
         <x:v>SRC-HCDN-KPI-090</x:v>
@@ -15518,7 +15518,7 @@
         <x:v>DATA-HCDN-00475</x:v>
       </x:c>
       <x:c r="I475" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J475" s="11" t="str">
         <x:v>SRC-HCDN-KPI-091</x:v>
@@ -15550,7 +15550,7 @@
         <x:v>DATA-HCDN-00476</x:v>
       </x:c>
       <x:c r="I476" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J476" s="11" t="str">
         <x:v>SRC-HCDN-KPI-092</x:v>
@@ -15582,7 +15582,7 @@
         <x:v>DATA-HCDN-00477</x:v>
       </x:c>
       <x:c r="I477" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J477" s="11" t="str">
         <x:v>SRC-HCDN-KPI-093</x:v>
@@ -15614,7 +15614,7 @@
         <x:v>DATA-HCDN-00478</x:v>
       </x:c>
       <x:c r="I478" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J478" s="11" t="str">
         <x:v>SRC-HCDN-KPI-094</x:v>
@@ -15646,7 +15646,7 @@
         <x:v>DATA-HCDN-00479</x:v>
       </x:c>
       <x:c r="I479" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J479" s="11" t="str">
         <x:v>SRC-HCDN-KPI-095</x:v>
@@ -15678,7 +15678,7 @@
         <x:v>DATA-HCDN-00480</x:v>
       </x:c>
       <x:c r="I480" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J480" s="11" t="str">
         <x:v>SRC-HCDN-KPI-096</x:v>
@@ -15695,7 +15695,7 @@
         <x:v>Actuarial</x:v>
       </x:c>
       <x:c r="D481" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E481" s="11" t="str">
         <x:v>exact</x:v>
@@ -15710,7 +15710,7 @@
         <x:v>DATA-HCDN-00481</x:v>
       </x:c>
       <x:c r="I481" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J481" s="11" t="str">
         <x:v>SRC-HCDN-KPI-001</x:v>
@@ -15721,13 +15721,13 @@
         <x:v>KPI-HCDN-0481</x:v>
       </x:c>
       <x:c r="B482" s="11" t="str">
-        <x:v>Medication adherence measure 0481</x:v>
+        <x:v>HEDIS medication adherence measure 0481</x:v>
       </x:c>
       <x:c r="C482" s="11" t="str">
         <x:v>Departmental Reporting</x:v>
       </x:c>
       <x:c r="D482" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E482" s="11" t="str">
         <x:v>range</x:v>
@@ -15742,7 +15742,7 @@
         <x:v>DATA-HCDN-00482</x:v>
       </x:c>
       <x:c r="I482" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J482" s="11" t="str">
         <x:v>SRC-HCDN-KPI-002</x:v>
@@ -15753,7 +15753,7 @@
         <x:v>KPI-HCDN-0482</x:v>
       </x:c>
       <x:c r="B483" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0482</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0482</x:v>
       </x:c>
       <x:c r="C483" s="11" t="str">
         <x:v>AI Transformation</x:v>
@@ -15774,7 +15774,7 @@
         <x:v>DATA-HCDN-00483</x:v>
       </x:c>
       <x:c r="I483" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J483" s="11" t="str">
         <x:v>SRC-HCDN-KPI-003</x:v>
@@ -15785,7 +15785,7 @@
         <x:v>KPI-HCDN-0483</x:v>
       </x:c>
       <x:c r="B484" s="11" t="str">
-        <x:v>Breast cancer screening measure 0483</x:v>
+        <x:v>HEDIS breast cancer screening measure 0483</x:v>
       </x:c>
       <x:c r="C484" s="11" t="str">
         <x:v>Technology</x:v>
@@ -15806,7 +15806,7 @@
         <x:v>DATA-HCDN-00484</x:v>
       </x:c>
       <x:c r="I484" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J484" s="11" t="str">
         <x:v>SRC-HCDN-KPI-004</x:v>
@@ -15838,7 +15838,7 @@
         <x:v>DATA-HCDN-00485</x:v>
       </x:c>
       <x:c r="I485" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J485" s="11" t="str">
         <x:v>SRC-HCDN-KPI-005</x:v>
@@ -15870,7 +15870,7 @@
         <x:v>DATA-HCDN-00486</x:v>
       </x:c>
       <x:c r="I486" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J486" s="11" t="str">
         <x:v>SRC-HCDN-KPI-006</x:v>
@@ -15902,7 +15902,7 @@
         <x:v>DATA-HCDN-00487</x:v>
       </x:c>
       <x:c r="I487" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J487" s="11" t="str">
         <x:v>SRC-HCDN-KPI-007</x:v>
@@ -15934,7 +15934,7 @@
         <x:v>DATA-HCDN-00488</x:v>
       </x:c>
       <x:c r="I488" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J488" s="11" t="str">
         <x:v>SRC-HCDN-KPI-008</x:v>
@@ -15951,7 +15951,7 @@
         <x:v>Privacy</x:v>
       </x:c>
       <x:c r="D489" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E489" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -15966,7 +15966,7 @@
         <x:v>DATA-HCDN-00489</x:v>
       </x:c>
       <x:c r="I489" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J489" s="11" t="str">
         <x:v>SRC-HCDN-KPI-009</x:v>
@@ -15983,7 +15983,7 @@
         <x:v>Compliance</x:v>
       </x:c>
       <x:c r="D490" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E490" s="11" t="str">
         <x:v>withheld</x:v>
@@ -15998,7 +15998,7 @@
         <x:v>DATA-HCDN-00490</x:v>
       </x:c>
       <x:c r="I490" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J490" s="11" t="str">
         <x:v>SRC-HCDN-KPI-010</x:v>
@@ -16030,7 +16030,7 @@
         <x:v>DATA-HCDN-00491</x:v>
       </x:c>
       <x:c r="I491" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J491" s="11" t="str">
         <x:v>SRC-HCDN-KPI-011</x:v>
@@ -16062,7 +16062,7 @@
         <x:v>DATA-HCDN-00492</x:v>
       </x:c>
       <x:c r="I492" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J492" s="11" t="str">
         <x:v>SRC-HCDN-KPI-012</x:v>
@@ -16094,7 +16094,7 @@
         <x:v>DATA-HCDN-00493</x:v>
       </x:c>
       <x:c r="I493" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J493" s="11" t="str">
         <x:v>SRC-HCDN-KPI-013</x:v>
@@ -16126,7 +16126,7 @@
         <x:v>DATA-HCDN-00494</x:v>
       </x:c>
       <x:c r="I494" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J494" s="11" t="str">
         <x:v>SRC-HCDN-KPI-014</x:v>
@@ -16158,7 +16158,7 @@
         <x:v>DATA-HCDN-00495</x:v>
       </x:c>
       <x:c r="I495" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J495" s="11" t="str">
         <x:v>SRC-HCDN-KPI-015</x:v>
@@ -16190,7 +16190,7 @@
         <x:v>DATA-HCDN-00496</x:v>
       </x:c>
       <x:c r="I496" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J496" s="11" t="str">
         <x:v>SRC-HCDN-KPI-016</x:v>
@@ -16207,7 +16207,7 @@
         <x:v>Population Health</x:v>
       </x:c>
       <x:c r="D497" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E497" s="11" t="str">
         <x:v>range</x:v>
@@ -16222,7 +16222,7 @@
         <x:v>DATA-HCDN-00497</x:v>
       </x:c>
       <x:c r="I497" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J497" s="11" t="str">
         <x:v>SRC-HCDN-KPI-017</x:v>
@@ -16239,7 +16239,7 @@
         <x:v>Health Plan Operations</x:v>
       </x:c>
       <x:c r="D498" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E498" s="11" t="str">
         <x:v>indexed</x:v>
@@ -16254,7 +16254,7 @@
         <x:v>DATA-HCDN-00498</x:v>
       </x:c>
       <x:c r="I498" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J498" s="11" t="str">
         <x:v>SRC-HCDN-KPI-018</x:v>
@@ -16286,7 +16286,7 @@
         <x:v>DATA-HCDN-00499</x:v>
       </x:c>
       <x:c r="I499" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J499" s="11" t="str">
         <x:v>SRC-HCDN-KPI-019</x:v>
@@ -16318,7 +16318,7 @@
         <x:v>DATA-HCDN-00500</x:v>
       </x:c>
       <x:c r="I500" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J500" s="11" t="str">
         <x:v>SRC-HCDN-KPI-020</x:v>
@@ -16350,7 +16350,7 @@
         <x:v>DATA-HCDN-00501</x:v>
       </x:c>
       <x:c r="I501" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J501" s="11" t="str">
         <x:v>SRC-HCDN-KPI-021</x:v>
@@ -16382,7 +16382,7 @@
         <x:v>DATA-HCDN-00502</x:v>
       </x:c>
       <x:c r="I502" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J502" s="11" t="str">
         <x:v>SRC-HCDN-KPI-022</x:v>
@@ -16414,7 +16414,7 @@
         <x:v>DATA-HCDN-00503</x:v>
       </x:c>
       <x:c r="I503" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J503" s="11" t="str">
         <x:v>SRC-HCDN-KPI-023</x:v>
@@ -16446,7 +16446,7 @@
         <x:v>DATA-HCDN-00504</x:v>
       </x:c>
       <x:c r="I504" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J504" s="11" t="str">
         <x:v>SRC-HCDN-KPI-024</x:v>
@@ -16463,7 +16463,7 @@
         <x:v>Care Management</x:v>
       </x:c>
       <x:c r="D505" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E505" s="11" t="str">
         <x:v>withheld</x:v>
@@ -16495,7 +16495,7 @@
         <x:v>Finance</x:v>
       </x:c>
       <x:c r="D506" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E506" s="11" t="str">
         <x:v>exact</x:v>
@@ -16670,7 +16670,7 @@
         <x:v>DATA-HCDN-00511</x:v>
       </x:c>
       <x:c r="I511" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J511" s="11" t="str">
         <x:v>SRC-HCDN-KPI-031</x:v>
@@ -16702,7 +16702,7 @@
         <x:v>DATA-HCDN-00512</x:v>
       </x:c>
       <x:c r="I512" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J512" s="11" t="str">
         <x:v>SRC-HCDN-KPI-032</x:v>
@@ -16719,7 +16719,7 @@
         <x:v>Inpatient</x:v>
       </x:c>
       <x:c r="D513" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E513" s="11" t="str">
         <x:v>indexed</x:v>
@@ -16734,7 +16734,7 @@
         <x:v>DATA-HCDN-00513</x:v>
       </x:c>
       <x:c r="I513" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J513" s="11" t="str">
         <x:v>SRC-HCDN-KPI-033</x:v>
@@ -16745,13 +16745,13 @@
         <x:v>KPI-HCDN-0513</x:v>
       </x:c>
       <x:c r="B514" s="11" t="str">
-        <x:v>Medication adherence measure 0513</x:v>
+        <x:v>HEDIS medication adherence measure 0513</x:v>
       </x:c>
       <x:c r="C514" s="11" t="str">
         <x:v>Surgery</x:v>
       </x:c>
       <x:c r="D514" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E514" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -16766,7 +16766,7 @@
         <x:v>DATA-HCDN-00514</x:v>
       </x:c>
       <x:c r="I514" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J514" s="11" t="str">
         <x:v>SRC-HCDN-KPI-034</x:v>
@@ -16777,7 +16777,7 @@
         <x:v>KPI-HCDN-0514</x:v>
       </x:c>
       <x:c r="B515" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0514</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0514</x:v>
       </x:c>
       <x:c r="C515" s="11" t="str">
         <x:v>Imaging</x:v>
@@ -16798,7 +16798,7 @@
         <x:v>DATA-HCDN-00515</x:v>
       </x:c>
       <x:c r="I515" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J515" s="11" t="str">
         <x:v>SRC-HCDN-KPI-035</x:v>
@@ -16809,7 +16809,7 @@
         <x:v>KPI-HCDN-0515</x:v>
       </x:c>
       <x:c r="B516" s="11" t="str">
-        <x:v>Breast cancer screening measure 0515</x:v>
+        <x:v>HEDIS breast cancer screening measure 0515</x:v>
       </x:c>
       <x:c r="C516" s="11" t="str">
         <x:v>Lab</x:v>
@@ -16830,7 +16830,7 @@
         <x:v>DATA-HCDN-00516</x:v>
       </x:c>
       <x:c r="I516" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J516" s="11" t="str">
         <x:v>SRC-HCDN-KPI-036</x:v>
@@ -16862,7 +16862,7 @@
         <x:v>DATA-HCDN-00517</x:v>
       </x:c>
       <x:c r="I517" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J517" s="11" t="str">
         <x:v>SRC-HCDN-KPI-037</x:v>
@@ -16894,7 +16894,7 @@
         <x:v>DATA-HCDN-00518</x:v>
       </x:c>
       <x:c r="I518" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J518" s="11" t="str">
         <x:v>SRC-HCDN-KPI-038</x:v>
@@ -16926,7 +16926,7 @@
         <x:v>DATA-HCDN-00519</x:v>
       </x:c>
       <x:c r="I519" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J519" s="11" t="str">
         <x:v>SRC-HCDN-KPI-039</x:v>
@@ -16958,7 +16958,7 @@
         <x:v>DATA-HCDN-00520</x:v>
       </x:c>
       <x:c r="I520" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J520" s="11" t="str">
         <x:v>SRC-HCDN-KPI-040</x:v>
@@ -16975,7 +16975,7 @@
         <x:v>Clinical Analytics</x:v>
       </x:c>
       <x:c r="D521" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E521" s="11" t="str">
         <x:v>exact</x:v>
@@ -16990,7 +16990,7 @@
         <x:v>DATA-HCDN-00521</x:v>
       </x:c>
       <x:c r="I521" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J521" s="11" t="str">
         <x:v>SRC-HCDN-KPI-041</x:v>
@@ -17007,7 +17007,7 @@
         <x:v>Actuarial</x:v>
       </x:c>
       <x:c r="D522" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E522" s="11" t="str">
         <x:v>range</x:v>
@@ -17022,7 +17022,7 @@
         <x:v>DATA-HCDN-00522</x:v>
       </x:c>
       <x:c r="I522" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J522" s="11" t="str">
         <x:v>SRC-HCDN-KPI-042</x:v>
@@ -17054,7 +17054,7 @@
         <x:v>DATA-HCDN-00523</x:v>
       </x:c>
       <x:c r="I523" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J523" s="11" t="str">
         <x:v>SRC-HCDN-KPI-043</x:v>
@@ -17086,7 +17086,7 @@
         <x:v>DATA-HCDN-00524</x:v>
       </x:c>
       <x:c r="I524" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J524" s="11" t="str">
         <x:v>SRC-HCDN-KPI-044</x:v>
@@ -17118,7 +17118,7 @@
         <x:v>DATA-HCDN-00525</x:v>
       </x:c>
       <x:c r="I525" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J525" s="11" t="str">
         <x:v>SRC-HCDN-KPI-045</x:v>
@@ -17150,7 +17150,7 @@
         <x:v>DATA-HCDN-00526</x:v>
       </x:c>
       <x:c r="I526" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J526" s="11" t="str">
         <x:v>SRC-HCDN-KPI-046</x:v>
@@ -17182,7 +17182,7 @@
         <x:v>DATA-HCDN-00527</x:v>
       </x:c>
       <x:c r="I527" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J527" s="11" t="str">
         <x:v>SRC-HCDN-KPI-047</x:v>
@@ -17214,7 +17214,7 @@
         <x:v>DATA-HCDN-00528</x:v>
       </x:c>
       <x:c r="I528" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J528" s="11" t="str">
         <x:v>SRC-HCDN-KPI-048</x:v>
@@ -17231,7 +17231,7 @@
         <x:v>Supply Chain</x:v>
       </x:c>
       <x:c r="D529" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E529" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -17246,7 +17246,7 @@
         <x:v>DATA-HCDN-00529</x:v>
       </x:c>
       <x:c r="I529" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J529" s="11" t="str">
         <x:v>SRC-HCDN-KPI-049</x:v>
@@ -17263,7 +17263,7 @@
         <x:v>Privacy</x:v>
       </x:c>
       <x:c r="D530" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E530" s="11" t="str">
         <x:v>withheld</x:v>
@@ -17278,7 +17278,7 @@
         <x:v>DATA-HCDN-00530</x:v>
       </x:c>
       <x:c r="I530" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J530" s="11" t="str">
         <x:v>SRC-HCDN-KPI-050</x:v>
@@ -17310,7 +17310,7 @@
         <x:v>DATA-HCDN-00531</x:v>
       </x:c>
       <x:c r="I531" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J531" s="11" t="str">
         <x:v>SRC-HCDN-KPI-051</x:v>
@@ -17342,7 +17342,7 @@
         <x:v>DATA-HCDN-00532</x:v>
       </x:c>
       <x:c r="I532" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J532" s="11" t="str">
         <x:v>SRC-HCDN-KPI-052</x:v>
@@ -17374,7 +17374,7 @@
         <x:v>DATA-HCDN-00533</x:v>
       </x:c>
       <x:c r="I533" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J533" s="11" t="str">
         <x:v>SRC-HCDN-KPI-053</x:v>
@@ -17406,7 +17406,7 @@
         <x:v>DATA-HCDN-00534</x:v>
       </x:c>
       <x:c r="I534" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J534" s="11" t="str">
         <x:v>SRC-HCDN-KPI-054</x:v>
@@ -17438,7 +17438,7 @@
         <x:v>DATA-HCDN-00535</x:v>
       </x:c>
       <x:c r="I535" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J535" s="11" t="str">
         <x:v>SRC-HCDN-KPI-055</x:v>
@@ -17470,7 +17470,7 @@
         <x:v>DATA-HCDN-00536</x:v>
       </x:c>
       <x:c r="I536" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J536" s="11" t="str">
         <x:v>SRC-HCDN-KPI-056</x:v>
@@ -17487,7 +17487,7 @@
         <x:v>Interoperability</x:v>
       </x:c>
       <x:c r="D537" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E537" s="11" t="str">
         <x:v>range</x:v>
@@ -17502,7 +17502,7 @@
         <x:v>DATA-HCDN-00537</x:v>
       </x:c>
       <x:c r="I537" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J537" s="11" t="str">
         <x:v>SRC-HCDN-KPI-057</x:v>
@@ -17519,7 +17519,7 @@
         <x:v>Population Health</x:v>
       </x:c>
       <x:c r="D538" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E538" s="11" t="str">
         <x:v>indexed</x:v>
@@ -17534,7 +17534,7 @@
         <x:v>DATA-HCDN-00538</x:v>
       </x:c>
       <x:c r="I538" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J538" s="11" t="str">
         <x:v>SRC-HCDN-KPI-058</x:v>
@@ -17566,7 +17566,7 @@
         <x:v>DATA-HCDN-00539</x:v>
       </x:c>
       <x:c r="I539" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J539" s="11" t="str">
         <x:v>SRC-HCDN-KPI-059</x:v>
@@ -17598,7 +17598,7 @@
         <x:v>DATA-HCDN-00540</x:v>
       </x:c>
       <x:c r="I540" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J540" s="11" t="str">
         <x:v>SRC-HCDN-KPI-060</x:v>
@@ -17630,7 +17630,7 @@
         <x:v>DATA-HCDN-00541</x:v>
       </x:c>
       <x:c r="I541" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J541" s="11" t="str">
         <x:v>SRC-HCDN-KPI-061</x:v>
@@ -17662,7 +17662,7 @@
         <x:v>DATA-HCDN-00542</x:v>
       </x:c>
       <x:c r="I542" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J542" s="11" t="str">
         <x:v>SRC-HCDN-KPI-062</x:v>
@@ -17694,7 +17694,7 @@
         <x:v>DATA-HCDN-00543</x:v>
       </x:c>
       <x:c r="I543" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J543" s="11" t="str">
         <x:v>SRC-HCDN-KPI-063</x:v>
@@ -17726,7 +17726,7 @@
         <x:v>DATA-HCDN-00544</x:v>
       </x:c>
       <x:c r="I544" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J544" s="11" t="str">
         <x:v>SRC-HCDN-KPI-064</x:v>
@@ -17743,7 +17743,7 @@
         <x:v>Risk Adjustment</x:v>
       </x:c>
       <x:c r="D545" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E545" s="11" t="str">
         <x:v>withheld</x:v>
@@ -17758,7 +17758,7 @@
         <x:v>DATA-HCDN-00545</x:v>
       </x:c>
       <x:c r="I545" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J545" s="11" t="str">
         <x:v>SRC-HCDN-KPI-065</x:v>
@@ -17769,13 +17769,13 @@
         <x:v>KPI-HCDN-0545</x:v>
       </x:c>
       <x:c r="B546" s="11" t="str">
-        <x:v>Medication adherence measure 0545</x:v>
+        <x:v>HEDIS medication adherence measure 0545</x:v>
       </x:c>
       <x:c r="C546" s="11" t="str">
         <x:v>Care Management</x:v>
       </x:c>
       <x:c r="D546" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E546" s="11" t="str">
         <x:v>exact</x:v>
@@ -17790,7 +17790,7 @@
         <x:v>DATA-HCDN-00546</x:v>
       </x:c>
       <x:c r="I546" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J546" s="11" t="str">
         <x:v>SRC-HCDN-KPI-066</x:v>
@@ -17801,7 +17801,7 @@
         <x:v>KPI-HCDN-0546</x:v>
       </x:c>
       <x:c r="B547" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0546</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0546</x:v>
       </x:c>
       <x:c r="C547" s="11" t="str">
         <x:v>Finance</x:v>
@@ -17833,7 +17833,7 @@
         <x:v>KPI-HCDN-0547</x:v>
       </x:c>
       <x:c r="B548" s="11" t="str">
-        <x:v>Breast cancer screening measure 0547</x:v>
+        <x:v>HEDIS breast cancer screening measure 0547</x:v>
       </x:c>
       <x:c r="C548" s="11" t="str">
         <x:v>Coding</x:v>
@@ -17999,7 +17999,7 @@
         <x:v>Emergency Department</x:v>
       </x:c>
       <x:c r="D553" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E553" s="11" t="str">
         <x:v>indexed</x:v>
@@ -18014,7 +18014,7 @@
         <x:v>DATA-HCDN-00553</x:v>
       </x:c>
       <x:c r="I553" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J553" s="11" t="str">
         <x:v>SRC-HCDN-KPI-073</x:v>
@@ -18031,7 +18031,7 @@
         <x:v>Inpatient</x:v>
       </x:c>
       <x:c r="D554" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E554" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -18046,7 +18046,7 @@
         <x:v>DATA-HCDN-00554</x:v>
       </x:c>
       <x:c r="I554" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J554" s="11" t="str">
         <x:v>SRC-HCDN-KPI-074</x:v>
@@ -18078,7 +18078,7 @@
         <x:v>DATA-HCDN-00555</x:v>
       </x:c>
       <x:c r="I555" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J555" s="11" t="str">
         <x:v>SRC-HCDN-KPI-075</x:v>
@@ -18110,7 +18110,7 @@
         <x:v>DATA-HCDN-00556</x:v>
       </x:c>
       <x:c r="I556" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J556" s="11" t="str">
         <x:v>SRC-HCDN-KPI-076</x:v>
@@ -18142,7 +18142,7 @@
         <x:v>DATA-HCDN-00557</x:v>
       </x:c>
       <x:c r="I557" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J557" s="11" t="str">
         <x:v>SRC-HCDN-KPI-077</x:v>
@@ -18174,7 +18174,7 @@
         <x:v>DATA-HCDN-00558</x:v>
       </x:c>
       <x:c r="I558" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J558" s="11" t="str">
         <x:v>SRC-HCDN-KPI-078</x:v>
@@ -18206,7 +18206,7 @@
         <x:v>DATA-HCDN-00559</x:v>
       </x:c>
       <x:c r="I559" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J559" s="11" t="str">
         <x:v>SRC-HCDN-KPI-079</x:v>
@@ -18238,7 +18238,7 @@
         <x:v>DATA-HCDN-00560</x:v>
       </x:c>
       <x:c r="I560" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J560" s="11" t="str">
         <x:v>SRC-HCDN-KPI-080</x:v>
@@ -18255,7 +18255,7 @@
         <x:v>Data and Analytics</x:v>
       </x:c>
       <x:c r="D561" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E561" s="11" t="str">
         <x:v>exact</x:v>
@@ -18270,7 +18270,7 @@
         <x:v>DATA-HCDN-00561</x:v>
       </x:c>
       <x:c r="I561" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J561" s="11" t="str">
         <x:v>SRC-HCDN-KPI-081</x:v>
@@ -18287,7 +18287,7 @@
         <x:v>Clinical Analytics</x:v>
       </x:c>
       <x:c r="D562" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E562" s="11" t="str">
         <x:v>range</x:v>
@@ -18302,7 +18302,7 @@
         <x:v>DATA-HCDN-00562</x:v>
       </x:c>
       <x:c r="I562" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J562" s="11" t="str">
         <x:v>SRC-HCDN-KPI-082</x:v>
@@ -18334,7 +18334,7 @@
         <x:v>DATA-HCDN-00563</x:v>
       </x:c>
       <x:c r="I563" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J563" s="11" t="str">
         <x:v>SRC-HCDN-KPI-083</x:v>
@@ -18366,7 +18366,7 @@
         <x:v>DATA-HCDN-00564</x:v>
       </x:c>
       <x:c r="I564" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J564" s="11" t="str">
         <x:v>SRC-HCDN-KPI-084</x:v>
@@ -18398,7 +18398,7 @@
         <x:v>DATA-HCDN-00565</x:v>
       </x:c>
       <x:c r="I565" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J565" s="11" t="str">
         <x:v>SRC-HCDN-KPI-085</x:v>
@@ -18430,7 +18430,7 @@
         <x:v>DATA-HCDN-00566</x:v>
       </x:c>
       <x:c r="I566" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J566" s="11" t="str">
         <x:v>SRC-HCDN-KPI-086</x:v>
@@ -18462,7 +18462,7 @@
         <x:v>DATA-HCDN-00567</x:v>
       </x:c>
       <x:c r="I567" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J567" s="11" t="str">
         <x:v>SRC-HCDN-KPI-087</x:v>
@@ -18494,7 +18494,7 @@
         <x:v>DATA-HCDN-00568</x:v>
       </x:c>
       <x:c r="I568" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J568" s="11" t="str">
         <x:v>SRC-HCDN-KPI-088</x:v>
@@ -18511,7 +18511,7 @@
         <x:v>HR</x:v>
       </x:c>
       <x:c r="D569" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E569" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -18526,7 +18526,7 @@
         <x:v>DATA-HCDN-00569</x:v>
       </x:c>
       <x:c r="I569" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J569" s="11" t="str">
         <x:v>SRC-HCDN-KPI-089</x:v>
@@ -18543,7 +18543,7 @@
         <x:v>Supply Chain</x:v>
       </x:c>
       <x:c r="D570" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E570" s="11" t="str">
         <x:v>withheld</x:v>
@@ -18558,7 +18558,7 @@
         <x:v>DATA-HCDN-00570</x:v>
       </x:c>
       <x:c r="I570" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J570" s="11" t="str">
         <x:v>SRC-HCDN-KPI-090</x:v>
@@ -18590,7 +18590,7 @@
         <x:v>DATA-HCDN-00571</x:v>
       </x:c>
       <x:c r="I571" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J571" s="11" t="str">
         <x:v>SRC-HCDN-KPI-091</x:v>
@@ -18622,7 +18622,7 @@
         <x:v>DATA-HCDN-00572</x:v>
       </x:c>
       <x:c r="I572" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J572" s="11" t="str">
         <x:v>SRC-HCDN-KPI-092</x:v>
@@ -18654,7 +18654,7 @@
         <x:v>DATA-HCDN-00573</x:v>
       </x:c>
       <x:c r="I573" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J573" s="11" t="str">
         <x:v>SRC-HCDN-KPI-093</x:v>
@@ -18686,7 +18686,7 @@
         <x:v>DATA-HCDN-00574</x:v>
       </x:c>
       <x:c r="I574" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J574" s="11" t="str">
         <x:v>SRC-HCDN-KPI-094</x:v>
@@ -18718,7 +18718,7 @@
         <x:v>DATA-HCDN-00575</x:v>
       </x:c>
       <x:c r="I575" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J575" s="11" t="str">
         <x:v>SRC-HCDN-KPI-095</x:v>
@@ -18750,7 +18750,7 @@
         <x:v>DATA-HCDN-00576</x:v>
       </x:c>
       <x:c r="I576" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J576" s="11" t="str">
         <x:v>SRC-HCDN-KPI-096</x:v>
@@ -18767,7 +18767,7 @@
         <x:v>Patient Access</x:v>
       </x:c>
       <x:c r="D577" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E577" s="11" t="str">
         <x:v>range</x:v>
@@ -18782,7 +18782,7 @@
         <x:v>DATA-HCDN-00577</x:v>
       </x:c>
       <x:c r="I577" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J577" s="11" t="str">
         <x:v>SRC-HCDN-KPI-001</x:v>
@@ -18793,13 +18793,13 @@
         <x:v>KPI-HCDN-0577</x:v>
       </x:c>
       <x:c r="B578" s="11" t="str">
-        <x:v>Medication adherence measure 0577</x:v>
+        <x:v>HEDIS medication adherence measure 0577</x:v>
       </x:c>
       <x:c r="C578" s="11" t="str">
         <x:v>Interoperability</x:v>
       </x:c>
       <x:c r="D578" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E578" s="11" t="str">
         <x:v>indexed</x:v>
@@ -18814,7 +18814,7 @@
         <x:v>DATA-HCDN-00578</x:v>
       </x:c>
       <x:c r="I578" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J578" s="11" t="str">
         <x:v>SRC-HCDN-KPI-002</x:v>
@@ -18825,7 +18825,7 @@
         <x:v>KPI-HCDN-0578</x:v>
       </x:c>
       <x:c r="B579" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0578</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0578</x:v>
       </x:c>
       <x:c r="C579" s="11" t="str">
         <x:v>Population Health</x:v>
@@ -18846,7 +18846,7 @@
         <x:v>DATA-HCDN-00579</x:v>
       </x:c>
       <x:c r="I579" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J579" s="11" t="str">
         <x:v>SRC-HCDN-KPI-003</x:v>
@@ -18857,7 +18857,7 @@
         <x:v>KPI-HCDN-0579</x:v>
       </x:c>
       <x:c r="B580" s="11" t="str">
-        <x:v>Breast cancer screening measure 0579</x:v>
+        <x:v>HEDIS breast cancer screening measure 0579</x:v>
       </x:c>
       <x:c r="C580" s="11" t="str">
         <x:v>Health Plan Operations</x:v>
@@ -18878,7 +18878,7 @@
         <x:v>DATA-HCDN-00580</x:v>
       </x:c>
       <x:c r="I580" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J580" s="11" t="str">
         <x:v>SRC-HCDN-KPI-004</x:v>
@@ -18910,7 +18910,7 @@
         <x:v>DATA-HCDN-00581</x:v>
       </x:c>
       <x:c r="I581" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J581" s="11" t="str">
         <x:v>SRC-HCDN-KPI-005</x:v>
@@ -18942,7 +18942,7 @@
         <x:v>DATA-HCDN-00582</x:v>
       </x:c>
       <x:c r="I582" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J582" s="11" t="str">
         <x:v>SRC-HCDN-KPI-006</x:v>
@@ -18974,7 +18974,7 @@
         <x:v>DATA-HCDN-00583</x:v>
       </x:c>
       <x:c r="I583" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J583" s="11" t="str">
         <x:v>SRC-HCDN-KPI-007</x:v>
@@ -19006,7 +19006,7 @@
         <x:v>DATA-HCDN-00584</x:v>
       </x:c>
       <x:c r="I584" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J584" s="11" t="str">
         <x:v>SRC-HCDN-KPI-008</x:v>
@@ -19023,7 +19023,7 @@
         <x:v>Quality and Stars</x:v>
       </x:c>
       <x:c r="D585" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E585" s="11" t="str">
         <x:v>withheld</x:v>
@@ -19038,7 +19038,7 @@
         <x:v>DATA-HCDN-00585</x:v>
       </x:c>
       <x:c r="I585" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J585" s="11" t="str">
         <x:v>SRC-HCDN-KPI-009</x:v>
@@ -19055,7 +19055,7 @@
         <x:v>Risk Adjustment</x:v>
       </x:c>
       <x:c r="D586" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E586" s="11" t="str">
         <x:v>exact</x:v>
@@ -19070,7 +19070,7 @@
         <x:v>DATA-HCDN-00586</x:v>
       </x:c>
       <x:c r="I586" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J586" s="11" t="str">
         <x:v>SRC-HCDN-KPI-010</x:v>
@@ -19102,7 +19102,7 @@
         <x:v>DATA-HCDN-00587</x:v>
       </x:c>
       <x:c r="I587" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J587" s="11" t="str">
         <x:v>SRC-HCDN-KPI-011</x:v>
@@ -19134,7 +19134,7 @@
         <x:v>DATA-HCDN-00588</x:v>
       </x:c>
       <x:c r="I588" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J588" s="11" t="str">
         <x:v>SRC-HCDN-KPI-012</x:v>
@@ -19279,7 +19279,7 @@
         <x:v>Ambulatory Care</x:v>
       </x:c>
       <x:c r="D593" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E593" s="11" t="str">
         <x:v>indexed</x:v>
@@ -19311,7 +19311,7 @@
         <x:v>Emergency Department</x:v>
       </x:c>
       <x:c r="D594" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E594" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -19358,7 +19358,7 @@
         <x:v>DATA-HCDN-00595</x:v>
       </x:c>
       <x:c r="I595" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J595" s="11" t="str">
         <x:v>SRC-HCDN-KPI-019</x:v>
@@ -19390,7 +19390,7 @@
         <x:v>DATA-HCDN-00596</x:v>
       </x:c>
       <x:c r="I596" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J596" s="11" t="str">
         <x:v>SRC-HCDN-KPI-020</x:v>
@@ -19422,7 +19422,7 @@
         <x:v>DATA-HCDN-00597</x:v>
       </x:c>
       <x:c r="I597" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J597" s="11" t="str">
         <x:v>SRC-HCDN-KPI-021</x:v>
@@ -19454,7 +19454,7 @@
         <x:v>DATA-HCDN-00598</x:v>
       </x:c>
       <x:c r="I598" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J598" s="11" t="str">
         <x:v>SRC-HCDN-KPI-022</x:v>
@@ -19486,7 +19486,7 @@
         <x:v>DATA-HCDN-00599</x:v>
       </x:c>
       <x:c r="I599" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J599" s="11" t="str">
         <x:v>SRC-HCDN-KPI-023</x:v>
@@ -19518,7 +19518,7 @@
         <x:v>DATA-HCDN-00600</x:v>
       </x:c>
       <x:c r="I600" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J600" s="11" t="str">
         <x:v>SRC-HCDN-KPI-024</x:v>
@@ -19535,7 +19535,7 @@
         <x:v>Cardiology</x:v>
       </x:c>
       <x:c r="D601" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E601" s="11" t="str">
         <x:v>exact</x:v>
@@ -19550,7 +19550,7 @@
         <x:v>DATA-HCDN-00601</x:v>
       </x:c>
       <x:c r="I601" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J601" s="11" t="str">
         <x:v>SRC-HCDN-KPI-025</x:v>
@@ -19567,7 +19567,7 @@
         <x:v>Data and Analytics</x:v>
       </x:c>
       <x:c r="D602" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E602" s="11" t="str">
         <x:v>range</x:v>
@@ -19582,7 +19582,7 @@
         <x:v>DATA-HCDN-00602</x:v>
       </x:c>
       <x:c r="I602" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J602" s="11" t="str">
         <x:v>SRC-HCDN-KPI-026</x:v>
@@ -19614,7 +19614,7 @@
         <x:v>DATA-HCDN-00603</x:v>
       </x:c>
       <x:c r="I603" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J603" s="11" t="str">
         <x:v>SRC-HCDN-KPI-027</x:v>
@@ -19646,7 +19646,7 @@
         <x:v>DATA-HCDN-00604</x:v>
       </x:c>
       <x:c r="I604" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J604" s="11" t="str">
         <x:v>SRC-HCDN-KPI-028</x:v>
@@ -19678,7 +19678,7 @@
         <x:v>DATA-HCDN-00605</x:v>
       </x:c>
       <x:c r="I605" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J605" s="11" t="str">
         <x:v>SRC-HCDN-KPI-029</x:v>
@@ -19710,7 +19710,7 @@
         <x:v>DATA-HCDN-00606</x:v>
       </x:c>
       <x:c r="I606" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J606" s="11" t="str">
         <x:v>SRC-HCDN-KPI-030</x:v>
@@ -19742,7 +19742,7 @@
         <x:v>DATA-HCDN-00607</x:v>
       </x:c>
       <x:c r="I607" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J607" s="11" t="str">
         <x:v>SRC-HCDN-KPI-031</x:v>
@@ -19774,7 +19774,7 @@
         <x:v>DATA-HCDN-00608</x:v>
       </x:c>
       <x:c r="I608" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J608" s="11" t="str">
         <x:v>SRC-HCDN-KPI-032</x:v>
@@ -19791,7 +19791,7 @@
         <x:v>Procurement</x:v>
       </x:c>
       <x:c r="D609" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E609" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -19806,7 +19806,7 @@
         <x:v>DATA-HCDN-00609</x:v>
       </x:c>
       <x:c r="I609" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J609" s="11" t="str">
         <x:v>SRC-HCDN-KPI-033</x:v>
@@ -19817,13 +19817,13 @@
         <x:v>KPI-HCDN-0609</x:v>
       </x:c>
       <x:c r="B610" s="11" t="str">
-        <x:v>Medication adherence measure 0609</x:v>
+        <x:v>HEDIS medication adherence measure 0609</x:v>
       </x:c>
       <x:c r="C610" s="11" t="str">
         <x:v>HR</x:v>
       </x:c>
       <x:c r="D610" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E610" s="11" t="str">
         <x:v>withheld</x:v>
@@ -19838,7 +19838,7 @@
         <x:v>DATA-HCDN-00610</x:v>
       </x:c>
       <x:c r="I610" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J610" s="11" t="str">
         <x:v>SRC-HCDN-KPI-034</x:v>
@@ -19849,7 +19849,7 @@
         <x:v>KPI-HCDN-0610</x:v>
       </x:c>
       <x:c r="B611" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0610</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0610</x:v>
       </x:c>
       <x:c r="C611" s="11" t="str">
         <x:v>Supply Chain</x:v>
@@ -19870,7 +19870,7 @@
         <x:v>DATA-HCDN-00611</x:v>
       </x:c>
       <x:c r="I611" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J611" s="11" t="str">
         <x:v>SRC-HCDN-KPI-035</x:v>
@@ -19881,7 +19881,7 @@
         <x:v>KPI-HCDN-0611</x:v>
       </x:c>
       <x:c r="B612" s="11" t="str">
-        <x:v>Breast cancer screening measure 0611</x:v>
+        <x:v>HEDIS breast cancer screening measure 0611</x:v>
       </x:c>
       <x:c r="C612" s="11" t="str">
         <x:v>Privacy</x:v>
@@ -19902,7 +19902,7 @@
         <x:v>DATA-HCDN-00612</x:v>
       </x:c>
       <x:c r="I612" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J612" s="11" t="str">
         <x:v>SRC-HCDN-KPI-036</x:v>
@@ -19934,7 +19934,7 @@
         <x:v>DATA-HCDN-00613</x:v>
       </x:c>
       <x:c r="I613" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J613" s="11" t="str">
         <x:v>SRC-HCDN-KPI-037</x:v>
@@ -19966,7 +19966,7 @@
         <x:v>DATA-HCDN-00614</x:v>
       </x:c>
       <x:c r="I614" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J614" s="11" t="str">
         <x:v>SRC-HCDN-KPI-038</x:v>
@@ -19998,7 +19998,7 @@
         <x:v>DATA-HCDN-00615</x:v>
       </x:c>
       <x:c r="I615" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J615" s="11" t="str">
         <x:v>SRC-HCDN-KPI-039</x:v>
@@ -20030,7 +20030,7 @@
         <x:v>DATA-HCDN-00616</x:v>
       </x:c>
       <x:c r="I616" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J616" s="11" t="str">
         <x:v>SRC-HCDN-KPI-040</x:v>
@@ -20047,7 +20047,7 @@
         <x:v>Revenue Cycle</x:v>
       </x:c>
       <x:c r="D617" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E617" s="11" t="str">
         <x:v>range</x:v>
@@ -20062,7 +20062,7 @@
         <x:v>DATA-HCDN-00617</x:v>
       </x:c>
       <x:c r="I617" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J617" s="11" t="str">
         <x:v>SRC-HCDN-KPI-041</x:v>
@@ -20079,7 +20079,7 @@
         <x:v>Patient Access</x:v>
       </x:c>
       <x:c r="D618" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E618" s="11" t="str">
         <x:v>indexed</x:v>
@@ -20094,7 +20094,7 @@
         <x:v>DATA-HCDN-00618</x:v>
       </x:c>
       <x:c r="I618" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J618" s="11" t="str">
         <x:v>SRC-HCDN-KPI-042</x:v>
@@ -20126,7 +20126,7 @@
         <x:v>DATA-HCDN-00619</x:v>
       </x:c>
       <x:c r="I619" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J619" s="11" t="str">
         <x:v>SRC-HCDN-KPI-043</x:v>
@@ -20158,7 +20158,7 @@
         <x:v>DATA-HCDN-00620</x:v>
       </x:c>
       <x:c r="I620" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J620" s="11" t="str">
         <x:v>SRC-HCDN-KPI-044</x:v>
@@ -20190,7 +20190,7 @@
         <x:v>DATA-HCDN-00621</x:v>
       </x:c>
       <x:c r="I621" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J621" s="11" t="str">
         <x:v>SRC-HCDN-KPI-045</x:v>
@@ -20222,7 +20222,7 @@
         <x:v>DATA-HCDN-00622</x:v>
       </x:c>
       <x:c r="I622" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J622" s="11" t="str">
         <x:v>SRC-HCDN-KPI-046</x:v>
@@ -20254,7 +20254,7 @@
         <x:v>DATA-HCDN-00623</x:v>
       </x:c>
       <x:c r="I623" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J623" s="11" t="str">
         <x:v>SRC-HCDN-KPI-047</x:v>
@@ -20286,7 +20286,7 @@
         <x:v>DATA-HCDN-00624</x:v>
       </x:c>
       <x:c r="I624" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J624" s="11" t="str">
         <x:v>SRC-HCDN-KPI-048</x:v>
@@ -20303,7 +20303,7 @@
         <x:v>Member Services</x:v>
       </x:c>
       <x:c r="D625" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E625" s="11" t="str">
         <x:v>withheld</x:v>
@@ -20318,7 +20318,7 @@
         <x:v>DATA-HCDN-00625</x:v>
       </x:c>
       <x:c r="I625" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J625" s="11" t="str">
         <x:v>SRC-HCDN-KPI-049</x:v>
@@ -20335,7 +20335,7 @@
         <x:v>Quality and Stars</x:v>
       </x:c>
       <x:c r="D626" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E626" s="11" t="str">
         <x:v>exact</x:v>
@@ -20350,7 +20350,7 @@
         <x:v>DATA-HCDN-00626</x:v>
       </x:c>
       <x:c r="I626" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J626" s="11" t="str">
         <x:v>SRC-HCDN-KPI-050</x:v>
@@ -20382,7 +20382,7 @@
         <x:v>DATA-HCDN-00627</x:v>
       </x:c>
       <x:c r="I627" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J627" s="11" t="str">
         <x:v>SRC-HCDN-KPI-051</x:v>
@@ -20414,7 +20414,7 @@
         <x:v>DATA-HCDN-00628</x:v>
       </x:c>
       <x:c r="I628" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J628" s="11" t="str">
         <x:v>SRC-HCDN-KPI-052</x:v>
@@ -20446,7 +20446,7 @@
         <x:v>DATA-HCDN-00629</x:v>
       </x:c>
       <x:c r="I629" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J629" s="11" t="str">
         <x:v>SRC-HCDN-KPI-053</x:v>
@@ -20478,7 +20478,7 @@
         <x:v>DATA-HCDN-00630</x:v>
       </x:c>
       <x:c r="I630" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J630" s="11" t="str">
         <x:v>SRC-HCDN-KPI-054</x:v>
@@ -20559,7 +20559,7 @@
         <x:v>Contact Center</x:v>
       </x:c>
       <x:c r="D633" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E633" s="11" t="str">
         <x:v>indexed</x:v>
@@ -20591,7 +20591,7 @@
         <x:v>Ambulatory Care</x:v>
       </x:c>
       <x:c r="D634" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E634" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -20702,7 +20702,7 @@
         <x:v>DATA-HCDN-00637</x:v>
       </x:c>
       <x:c r="I637" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J637" s="11" t="str">
         <x:v>SRC-HCDN-KPI-061</x:v>
@@ -20734,7 +20734,7 @@
         <x:v>DATA-HCDN-00638</x:v>
       </x:c>
       <x:c r="I638" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J638" s="11" t="str">
         <x:v>SRC-HCDN-KPI-062</x:v>
@@ -20766,7 +20766,7 @@
         <x:v>DATA-HCDN-00639</x:v>
       </x:c>
       <x:c r="I639" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J639" s="11" t="str">
         <x:v>SRC-HCDN-KPI-063</x:v>
@@ -20798,7 +20798,7 @@
         <x:v>DATA-HCDN-00640</x:v>
       </x:c>
       <x:c r="I640" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J640" s="11" t="str">
         <x:v>SRC-HCDN-KPI-064</x:v>
@@ -20815,7 +20815,7 @@
         <x:v>Oncology</x:v>
       </x:c>
       <x:c r="D641" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E641" s="11" t="str">
         <x:v>exact</x:v>
@@ -20830,7 +20830,7 @@
         <x:v>DATA-HCDN-00641</x:v>
       </x:c>
       <x:c r="I641" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J641" s="11" t="str">
         <x:v>SRC-HCDN-KPI-065</x:v>
@@ -20841,13 +20841,13 @@
         <x:v>KPI-HCDN-0641</x:v>
       </x:c>
       <x:c r="B642" s="11" t="str">
-        <x:v>Medication adherence measure 0641</x:v>
+        <x:v>HEDIS medication adherence measure 0641</x:v>
       </x:c>
       <x:c r="C642" s="11" t="str">
         <x:v>Cardiology</x:v>
       </x:c>
       <x:c r="D642" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E642" s="11" t="str">
         <x:v>range</x:v>
@@ -20862,7 +20862,7 @@
         <x:v>DATA-HCDN-00642</x:v>
       </x:c>
       <x:c r="I642" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J642" s="11" t="str">
         <x:v>SRC-HCDN-KPI-066</x:v>
@@ -20873,7 +20873,7 @@
         <x:v>KPI-HCDN-0642</x:v>
       </x:c>
       <x:c r="B643" s="11" t="str">
-        <x:v>Diabetes HbA1c control measure 0642</x:v>
+        <x:v>HEDIS diabetes HbA1c control measure 0642</x:v>
       </x:c>
       <x:c r="C643" s="11" t="str">
         <x:v>Data and Analytics</x:v>
@@ -20894,7 +20894,7 @@
         <x:v>DATA-HCDN-00643</x:v>
       </x:c>
       <x:c r="I643" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J643" s="11" t="str">
         <x:v>SRC-HCDN-KPI-067</x:v>
@@ -20905,7 +20905,7 @@
         <x:v>KPI-HCDN-0643</x:v>
       </x:c>
       <x:c r="B644" s="11" t="str">
-        <x:v>Breast cancer screening measure 0643</x:v>
+        <x:v>HEDIS breast cancer screening measure 0643</x:v>
       </x:c>
       <x:c r="C644" s="11" t="str">
         <x:v>Clinical Analytics</x:v>
@@ -20926,7 +20926,7 @@
         <x:v>DATA-HCDN-00644</x:v>
       </x:c>
       <x:c r="I644" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J644" s="11" t="str">
         <x:v>SRC-HCDN-KPI-068</x:v>
@@ -20958,7 +20958,7 @@
         <x:v>DATA-HCDN-00645</x:v>
       </x:c>
       <x:c r="I645" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>numerator in source</x:v>
       </x:c>
       <x:c r="J645" s="11" t="str">
         <x:v>SRC-HCDN-KPI-069</x:v>
@@ -20990,7 +20990,7 @@
         <x:v>DATA-HCDN-00646</x:v>
       </x:c>
       <x:c r="I646" s="11" t="str">
-        <x:v>latency to confirm</x:v>
+        <x:v>denominator in source</x:v>
       </x:c>
       <x:c r="J646" s="11" t="str">
         <x:v>SRC-HCDN-KPI-070</x:v>
@@ -21022,7 +21022,7 @@
         <x:v>DATA-HCDN-00647</x:v>
       </x:c>
       <x:c r="I647" s="11" t="str">
-        <x:v>regulatory use</x:v>
+        <x:v>exclusions to confirm</x:v>
       </x:c>
       <x:c r="J647" s="11" t="str">
         <x:v>SRC-HCDN-KPI-071</x:v>
@@ -21054,7 +21054,7 @@
         <x:v>DATA-HCDN-00648</x:v>
       </x:c>
       <x:c r="I648" s="11" t="str">
-        <x:v>contractual incentive use</x:v>
+        <x:v>latency to confirm</x:v>
       </x:c>
       <x:c r="J648" s="11" t="str">
         <x:v>SRC-HCDN-KPI-072</x:v>
@@ -21071,7 +21071,7 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D649" s="11" t="str">
-        <x:v>Medicare Advantage</x:v>
+        <x:v>Medicare Advantage - tenant-specific approx 80% Medicare/MA covered lives</x:v>
       </x:c>
       <x:c r="E649" s="11" t="str">
         <x:v>trend-only</x:v>
@@ -21086,7 +21086,7 @@
         <x:v>DATA-HCDN-00649</x:v>
       </x:c>
       <x:c r="I649" s="11" t="str">
-        <x:v>numerator in source</x:v>
+        <x:v>regulatory use</x:v>
       </x:c>
       <x:c r="J649" s="11" t="str">
         <x:v>SRC-HCDN-KPI-073</x:v>
@@ -21103,7 +21103,7 @@
         <x:v>Procurement</x:v>
       </x:c>
       <x:c r="D650" s="11" t="str">
-        <x:v>Commercial</x:v>
+        <x:v>Commercial minority population</x:v>
       </x:c>
       <x:c r="E650" s="11" t="str">
         <x:v>withheld</x:v>
@@ -21118,7 +21118,7 @@
         <x:v>DATA-HCDN-00650</x:v>
       </x:c>
       <x:c r="I650" s="11" t="str">
-        <x:v>denominator in source</x:v>
+        <x:v>contractual incentive use</x:v>
       </x:c>
       <x:c r="J650" s="11" t="str">
         <x:v>SRC-HCDN-KPI-074</x:v>
@@ -21150,7 +21150,7 @@
         <x:v>DATA-HCDN-00651</x:v>
       </x:c>
       <x:c r="I651" s="11" t="str">
-        <x:v>exclusions to confirm</x:v>
+        <x:v>tenant-specific Medicare/MA assumption boundary</x:v>
       </x:c>
       <x:c r="J651" s="11" t="str">
         <x:v>SRC-HCDN-KPI-075</x:v>
